--- a/Dados/PRODUTIVIDADE/table_PROD_TRIM_RS.xlsx
+++ b/Dados/PRODUTIVIDADE/table_PROD_TRIM_RS.xlsx
@@ -54840,7 +54840,7 @@
         <v>92.21769737034285</v>
       </c>
       <c r="F5">
-        <v>26.15657762972751</v>
+        <v>26.1565776297275</v>
       </c>
       <c r="G5">
         <v>56.62376003927254</v>
@@ -54904,7 +54904,7 @@
         <v>25.49928026022375</v>
       </c>
       <c r="G6">
-        <v>56.40850236786488</v>
+        <v>56.40850236786486</v>
       </c>
       <c r="H6">
         <v>28.72481952546692</v>
@@ -54937,7 +54937,7 @@
         <v>40.42241260070236</v>
       </c>
       <c r="R6">
-        <v>43.10828274698906</v>
+        <v>43.10828274698905</v>
       </c>
       <c r="S6">
         <v>40.17496447278526</v>
@@ -54983,16 +54983,16 @@
         <v>417.5543135794594</v>
       </c>
       <c r="M7">
-        <v>32.47376963435394</v>
+        <v>32.47376963435393</v>
       </c>
       <c r="N7">
         <v>75.18399703567636</v>
       </c>
       <c r="O7">
-        <v>47.22381551661695</v>
+        <v>47.22381551661694</v>
       </c>
       <c r="P7">
-        <v>48.29623009190399</v>
+        <v>48.29623009190398</v>
       </c>
       <c r="Q7">
         <v>42.86713568008683</v>
@@ -55020,28 +55020,28 @@
         <v>72.66480640089588</v>
       </c>
       <c r="E8">
-        <v>92.64391218728302</v>
+        <v>92.64391218728301</v>
       </c>
       <c r="F8">
         <v>26.14645530983375</v>
       </c>
       <c r="G8">
-        <v>59.07485484112306</v>
+        <v>59.07485484112307</v>
       </c>
       <c r="H8">
-        <v>28.75327524167829</v>
+        <v>28.7532752416783</v>
       </c>
       <c r="I8">
-        <v>28.47551882740478</v>
+        <v>28.47551882740479</v>
       </c>
       <c r="J8">
-        <v>80.62876456037908</v>
+        <v>80.6287645603791</v>
       </c>
       <c r="K8">
         <v>203.9897146611027</v>
       </c>
       <c r="L8">
-        <v>393.9810984239157</v>
+        <v>393.9810984239158</v>
       </c>
       <c r="M8">
         <v>32.54648741271837</v>
@@ -55059,7 +55059,7 @@
         <v>43.2135231996615</v>
       </c>
       <c r="R8">
-        <v>44.27569869945533</v>
+        <v>44.27569869945534</v>
       </c>
       <c r="S8">
         <v>41.27616765214386</v>
@@ -55078,7 +55078,7 @@
         <v>33.16967022612681</v>
       </c>
       <c r="D9">
-        <v>73.51647216659163</v>
+        <v>73.51647216659161</v>
       </c>
       <c r="E9">
         <v>98.50129801123694</v>
@@ -55090,13 +55090,13 @@
         <v>59.81795749937199</v>
       </c>
       <c r="H9">
-        <v>28.56254323739037</v>
+        <v>28.56254323739036</v>
       </c>
       <c r="I9">
         <v>29.43758198616769</v>
       </c>
       <c r="J9">
-        <v>80.7818294826243</v>
+        <v>80.78182948262432</v>
       </c>
       <c r="K9">
         <v>207.4189104399784</v>
@@ -55172,7 +55172,7 @@
         <v>75.39393595673054</v>
       </c>
       <c r="O10">
-        <v>47.08806045104205</v>
+        <v>47.08806045104204</v>
       </c>
       <c r="P10">
         <v>49.0078629736885</v>
@@ -55184,7 +55184,7 @@
         <v>44.35876142690236</v>
       </c>
       <c r="S10">
-        <v>41.29972956921705</v>
+        <v>41.29972956921706</v>
       </c>
     </row>
     <row r="11">
@@ -55200,7 +55200,7 @@
         <v>39.07036328653987</v>
       </c>
       <c r="D11">
-        <v>72.4551355185329</v>
+        <v>72.45513551853288</v>
       </c>
       <c r="E11">
         <v>113.4489197556044</v>
@@ -55245,7 +55245,7 @@
         <v>43.86604986600963</v>
       </c>
       <c r="S11">
-        <v>40.78600207157014</v>
+        <v>40.78600207157012</v>
       </c>
     </row>
     <row r="12">
@@ -55258,7 +55258,7 @@
         <v>40.89953052610582</v>
       </c>
       <c r="C12">
-        <v>40.30418657667686</v>
+        <v>40.30418657667685</v>
       </c>
       <c r="D12">
         <v>71.51164264355768</v>
@@ -55306,7 +55306,7 @@
         <v>43.6902623923506</v>
       </c>
       <c r="S12">
-        <v>40.61276334355105</v>
+        <v>40.61276334355104</v>
       </c>
     </row>
     <row r="13">
@@ -55355,7 +55355,7 @@
         <v>76.59607683637338</v>
       </c>
       <c r="O13">
-        <v>47.00213193138981</v>
+        <v>47.0021319313898</v>
       </c>
       <c r="P13">
         <v>48.8557397741431</v>
@@ -55364,7 +55364,7 @@
         <v>43.17796684430301</v>
       </c>
       <c r="R13">
-        <v>43.50724312624825</v>
+        <v>43.50724312624824</v>
       </c>
       <c r="S13">
         <v>40.41638014383436</v>
@@ -55380,7 +55380,7 @@
         <v>41.6414935081691</v>
       </c>
       <c r="C14">
-        <v>40.48824248636705</v>
+        <v>40.48824248636704</v>
       </c>
       <c r="D14">
         <v>70.01916331467879</v>
@@ -55407,7 +55407,7 @@
         <v>218.6990748984418</v>
       </c>
       <c r="L14">
-        <v>495.4892343405623</v>
+        <v>495.4892343405622</v>
       </c>
       <c r="M14">
         <v>29.94500258724677</v>
@@ -55425,10 +55425,10 @@
         <v>42.77154977049661</v>
       </c>
       <c r="R14">
-        <v>42.95286622624488</v>
+        <v>42.95286622624487</v>
       </c>
       <c r="S14">
-        <v>39.89544792004819</v>
+        <v>39.89544792004818</v>
       </c>
     </row>
     <row r="15">
@@ -55471,10 +55471,10 @@
         <v>473.790198579323</v>
       </c>
       <c r="M15">
-        <v>29.91868062527817</v>
+        <v>29.91868062527818</v>
       </c>
       <c r="N15">
-        <v>75.66999978312901</v>
+        <v>75.66999978312903</v>
       </c>
       <c r="O15">
         <v>46.14909491412862</v>
@@ -55502,7 +55502,7 @@
         <v>45.3527279331269</v>
       </c>
       <c r="C16">
-        <v>33.17278053511153</v>
+        <v>33.17278053511152</v>
       </c>
       <c r="D16">
         <v>67.49878183663742</v>
@@ -55514,13 +55514,13 @@
         <v>25.96366893369163</v>
       </c>
       <c r="G16">
-        <v>56.18576144434682</v>
+        <v>56.18576144434683</v>
       </c>
       <c r="H16">
         <v>27.71093518080691</v>
       </c>
       <c r="I16">
-        <v>30.79078357068895</v>
+        <v>30.79078357068894</v>
       </c>
       <c r="J16">
         <v>67.42050608535536</v>
@@ -55547,7 +55547,7 @@
         <v>42.08073159096017</v>
       </c>
       <c r="R16">
-        <v>41.55926989569285</v>
+        <v>41.55926989569286</v>
       </c>
       <c r="S16">
         <v>38.50385634205182</v>
@@ -55642,7 +55642,7 @@
         <v>26.41902897495148</v>
       </c>
       <c r="I18">
-        <v>28.24429986443</v>
+        <v>28.24429986443001</v>
       </c>
       <c r="J18">
         <v>66.40014446252906</v>
@@ -55660,16 +55660,16 @@
         <v>74.5483726257219</v>
       </c>
       <c r="O18">
-        <v>44.95735429388497</v>
+        <v>44.95735429388498</v>
       </c>
       <c r="P18">
         <v>46.83975677349998</v>
       </c>
       <c r="Q18">
-        <v>40.78779645493938</v>
+        <v>40.78779645493937</v>
       </c>
       <c r="R18">
-        <v>40.18693002785592</v>
+        <v>40.18693002785591</v>
       </c>
       <c r="S18">
         <v>37.13643514091318</v>
@@ -55688,7 +55688,7 @@
         <v>30.36613528893835</v>
       </c>
       <c r="D19">
-        <v>63.80546088089947</v>
+        <v>63.80546088089946</v>
       </c>
       <c r="E19">
         <v>94.73806855306901</v>
@@ -55712,7 +55712,7 @@
         <v>211.9545261601349</v>
       </c>
       <c r="L19">
-        <v>558.9731789806597</v>
+        <v>558.9731789806598</v>
       </c>
       <c r="M19">
         <v>30.09623527487827</v>
@@ -55764,7 +55764,7 @@
         <v>26.36683263072401</v>
       </c>
       <c r="I20">
-        <v>28.38740304515686</v>
+        <v>28.38740304515685</v>
       </c>
       <c r="J20">
         <v>72.29341622091444</v>
@@ -55773,7 +55773,7 @@
         <v>200.6984081817866</v>
       </c>
       <c r="L20">
-        <v>550.3091807364061</v>
+        <v>550.309180736406</v>
       </c>
       <c r="M20">
         <v>30.01451490362795</v>
@@ -55807,7 +55807,7 @@
         <v>44.50474693540819</v>
       </c>
       <c r="C21">
-        <v>30.94600100987598</v>
+        <v>30.94600100987599</v>
       </c>
       <c r="D21">
         <v>64.6075289305024</v>
@@ -55822,7 +55822,7 @@
         <v>53.13445933973635</v>
       </c>
       <c r="H21">
-        <v>26.52412674148364</v>
+        <v>26.52412674148365</v>
       </c>
       <c r="I21">
         <v>28.9824654474837</v>
@@ -55846,7 +55846,7 @@
         <v>45.09086190098724</v>
       </c>
       <c r="P21">
-        <v>46.81347826504694</v>
+        <v>46.81347826504695</v>
       </c>
       <c r="Q21">
         <v>40.71741935543292</v>
@@ -55855,7 +55855,7 @@
         <v>40.0890969943861</v>
       </c>
       <c r="S21">
-        <v>37.13012338694425</v>
+        <v>37.13012338694426</v>
       </c>
     </row>
     <row r="22">
@@ -55877,7 +55877,7 @@
         <v>104.9987145699433</v>
       </c>
       <c r="F22">
-        <v>23.16635328235271</v>
+        <v>23.16635328235272</v>
       </c>
       <c r="G22">
         <v>53.77037814369057</v>
@@ -55898,7 +55898,7 @@
         <v>500.3588745065266</v>
       </c>
       <c r="M22">
-        <v>29.51123126428793</v>
+        <v>29.51123126428792</v>
       </c>
       <c r="N22">
         <v>73.88850730558011</v>
@@ -55913,7 +55913,7 @@
         <v>41.2848545590444</v>
       </c>
       <c r="R22">
-        <v>40.17607851065148</v>
+        <v>40.17607851065147</v>
       </c>
       <c r="S22">
         <v>37.22458228923785</v>
@@ -55950,7 +55950,7 @@
         <v>29.18597354081619</v>
       </c>
       <c r="J23">
-        <v>79.31226481635463</v>
+        <v>79.31226481635461</v>
       </c>
       <c r="K23">
         <v>197.1450876072753</v>
@@ -55974,7 +55974,7 @@
         <v>41.7146229363219</v>
       </c>
       <c r="R23">
-        <v>40.28669643934054</v>
+        <v>40.28669643934053</v>
       </c>
       <c r="S23">
         <v>37.29763250471073</v>
@@ -55990,13 +55990,13 @@
         <v>50.30876910758272</v>
       </c>
       <c r="C24">
-        <v>36.49008693163664</v>
+        <v>36.49008693163665</v>
       </c>
       <c r="D24">
         <v>66.54874154759511</v>
       </c>
       <c r="E24">
-        <v>92.6687441177198</v>
+        <v>92.66874411771981</v>
       </c>
       <c r="F24">
         <v>23.89279042865898</v>
@@ -56014,7 +56014,7 @@
         <v>80.20148221494387</v>
       </c>
       <c r="K24">
-        <v>202.6203263963114</v>
+        <v>202.6203263963113</v>
       </c>
       <c r="L24">
         <v>438.1074754690164</v>
@@ -56075,16 +56075,16 @@
         <v>80.69965677989082</v>
       </c>
       <c r="K25">
-        <v>210.3485632163202</v>
+        <v>210.3485632163203</v>
       </c>
       <c r="L25">
-        <v>460.6973596660964</v>
+        <v>460.6973596660963</v>
       </c>
       <c r="M25">
         <v>29.16610613858489</v>
       </c>
       <c r="N25">
-        <v>74.15106758255261</v>
+        <v>74.15106758255259</v>
       </c>
       <c r="O25">
         <v>45.25673921965556</v>
@@ -56109,7 +56109,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>49.89928124914539</v>
+        <v>49.89928124914537</v>
       </c>
       <c r="C26">
         <v>30.66803672138668</v>
@@ -56121,10 +56121,10 @@
         <v>87.31033705878848</v>
       </c>
       <c r="F26">
-        <v>23.69314253510737</v>
+        <v>23.69314253510738</v>
       </c>
       <c r="G26">
-        <v>54.95373142518154</v>
+        <v>54.95373142518152</v>
       </c>
       <c r="H26">
         <v>28.32773333347483</v>
@@ -56160,7 +56160,7 @@
         <v>40.91841011227008</v>
       </c>
       <c r="S26">
-        <v>37.75629744223323</v>
+        <v>37.75629744223322</v>
       </c>
     </row>
     <row r="27">
@@ -56170,13 +56170,13 @@
         </is>
       </c>
       <c r="B27">
-        <v>48.88793040823106</v>
+        <v>48.88793040823105</v>
       </c>
       <c r="C27">
-        <v>30.42325253633061</v>
+        <v>30.4232525363306</v>
       </c>
       <c r="D27">
-        <v>66.22752182894864</v>
+        <v>66.22752182894865</v>
       </c>
       <c r="E27">
         <v>84.62842712590114</v>
@@ -56185,7 +56185,7 @@
         <v>23.08969260306598</v>
       </c>
       <c r="G27">
-        <v>53.81387378006416</v>
+        <v>53.81387378006417</v>
       </c>
       <c r="H27">
         <v>28.93416073120988</v>
@@ -56215,7 +56215,7 @@
         <v>48.01341773730893</v>
       </c>
       <c r="Q27">
-        <v>42.09703944091754</v>
+        <v>42.09703944091755</v>
       </c>
       <c r="R27">
         <v>41.03046879004989</v>
@@ -56246,7 +56246,7 @@
         <v>22.6302887537982</v>
       </c>
       <c r="G28">
-        <v>54.72474297328399</v>
+        <v>54.724742973284</v>
       </c>
       <c r="H28">
         <v>29.47453232551909</v>
@@ -56261,7 +56261,7 @@
         <v>236.5148204847233</v>
       </c>
       <c r="L28">
-        <v>508.4543910087741</v>
+        <v>508.4543910087742</v>
       </c>
       <c r="M28">
         <v>30.42338555060801</v>
@@ -56298,10 +56298,10 @@
         <v>37.97629030785146</v>
       </c>
       <c r="D29">
-        <v>69.44163814325125</v>
+        <v>69.44163814325127</v>
       </c>
       <c r="E29">
-        <v>91.73628868803061</v>
+        <v>91.73628868803063</v>
       </c>
       <c r="F29">
         <v>22.28232896921338</v>
@@ -56353,7 +56353,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>48.64358456620715</v>
+        <v>48.64358456620713</v>
       </c>
       <c r="C30">
         <v>44.9060094258375</v>
@@ -56374,10 +56374,10 @@
         <v>29.8578599318708</v>
       </c>
       <c r="I30">
-        <v>29.38560725797773</v>
+        <v>29.38560725797772</v>
       </c>
       <c r="J30">
-        <v>67.89254773664125</v>
+        <v>67.89254773664126</v>
       </c>
       <c r="K30">
         <v>254.7729392558894</v>
@@ -56404,7 +56404,7 @@
         <v>42.20374853626665</v>
       </c>
       <c r="S30">
-        <v>38.84996069108793</v>
+        <v>38.84996069108794</v>
       </c>
     </row>
     <row r="31">
@@ -56417,7 +56417,7 @@
         <v>50.18861059215352</v>
       </c>
       <c r="C31">
-        <v>45.41763559392666</v>
+        <v>45.41763559392667</v>
       </c>
       <c r="D31">
         <v>72.37331521212037</v>
@@ -56453,10 +56453,10 @@
         <v>70.70132329060689</v>
       </c>
       <c r="O31">
-        <v>46.07334393373346</v>
+        <v>46.07334393373345</v>
       </c>
       <c r="P31">
-        <v>49.36604312743606</v>
+        <v>49.36604312743607</v>
       </c>
       <c r="Q31">
         <v>43.32396743717922</v>
@@ -56481,7 +56481,7 @@
         <v>40.97012535653651</v>
       </c>
       <c r="D32">
-        <v>71.90972349762797</v>
+        <v>71.90972349762798</v>
       </c>
       <c r="E32">
         <v>102.2861264409253</v>
@@ -56499,19 +56499,19 @@
         <v>27.46325031136869</v>
       </c>
       <c r="J32">
-        <v>62.38416706682949</v>
+        <v>62.3841670668295</v>
       </c>
       <c r="K32">
         <v>262.1517799700889</v>
       </c>
       <c r="L32">
-        <v>524.7088974086889</v>
+        <v>524.7088974086888</v>
       </c>
       <c r="M32">
         <v>29.19045899213194</v>
       </c>
       <c r="N32">
-        <v>69.95510149190703</v>
+        <v>69.95510149190702</v>
       </c>
       <c r="O32">
         <v>45.61096436867142</v>
@@ -56526,7 +56526,7 @@
         <v>41.84260310226308</v>
       </c>
       <c r="S32">
-        <v>38.47669967404592</v>
+        <v>38.47669967404593</v>
       </c>
     </row>
     <row r="33">
@@ -56536,13 +56536,13 @@
         </is>
       </c>
       <c r="B33">
-        <v>51.21926506981521</v>
+        <v>51.21926506981523</v>
       </c>
       <c r="C33">
         <v>34.95981139708514</v>
       </c>
       <c r="D33">
-        <v>70.02310052921787</v>
+        <v>70.02310052921786</v>
       </c>
       <c r="E33">
         <v>112.3837233380878</v>
@@ -56566,7 +56566,7 @@
         <v>274.7537261494709</v>
       </c>
       <c r="L33">
-        <v>531.1099612630217</v>
+        <v>531.1099612630215</v>
       </c>
       <c r="M33">
         <v>29.13163273179169</v>
@@ -56587,7 +56587,7 @@
         <v>41.3318725178476</v>
       </c>
       <c r="S33">
-        <v>37.8936447037218</v>
+        <v>37.89364470372181</v>
       </c>
     </row>
     <row r="34">
@@ -56627,13 +56627,13 @@
         <v>287.6820374672967</v>
       </c>
       <c r="L34">
-        <v>565.3558085883607</v>
+        <v>565.3558085883608</v>
       </c>
       <c r="M34">
         <v>29.08276408594</v>
       </c>
       <c r="N34">
-        <v>68.20352695102005</v>
+        <v>68.20352695102004</v>
       </c>
       <c r="O34">
         <v>45.09247777574486</v>
@@ -56645,7 +56645,7 @@
         <v>42.272994892387</v>
       </c>
       <c r="R34">
-        <v>41.07426400008072</v>
+        <v>41.07426400008073</v>
       </c>
       <c r="S34">
         <v>37.57847037135468</v>
@@ -56658,7 +56658,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>37.99854661842644</v>
+        <v>37.99854661842645</v>
       </c>
       <c r="C35">
         <v>38.2620820520366</v>
@@ -56694,7 +56694,7 @@
         <v>28.32294996370109</v>
       </c>
       <c r="N35">
-        <v>67.32260246611733</v>
+        <v>67.32260246611732</v>
       </c>
       <c r="O35">
         <v>45.05115337664939</v>
@@ -56722,7 +56722,7 @@
         <v>37.30779871157479</v>
       </c>
       <c r="C36">
-        <v>42.13831044893726</v>
+        <v>42.13831044893727</v>
       </c>
       <c r="D36">
         <v>68.27355553190806</v>
@@ -56740,7 +56740,7 @@
         <v>30.15436011452956</v>
       </c>
       <c r="I36">
-        <v>23.77131652730965</v>
+        <v>23.77131652730964</v>
       </c>
       <c r="J36">
         <v>62.0208389619046</v>
@@ -56752,7 +56752,7 @@
         <v>644.8984992868135</v>
       </c>
       <c r="M36">
-        <v>28.48834536633053</v>
+        <v>28.48834536633052</v>
       </c>
       <c r="N36">
         <v>67.62384026545806</v>
@@ -56783,7 +56783,7 @@
         <v>34.91611053187442</v>
       </c>
       <c r="C37">
-        <v>51.48083146434858</v>
+        <v>51.48083146434859</v>
       </c>
       <c r="D37">
         <v>72.86380985906526</v>
@@ -56810,13 +56810,13 @@
         <v>248.3620372917873</v>
       </c>
       <c r="L37">
-        <v>760.9716647905934</v>
+        <v>760.9716647905933</v>
       </c>
       <c r="M37">
         <v>29.06845903896379</v>
       </c>
       <c r="N37">
-        <v>67.69634273656284</v>
+        <v>67.69634273656283</v>
       </c>
       <c r="O37">
         <v>46.64284751242155</v>
@@ -56828,7 +56828,7 @@
         <v>41.62243096026806</v>
       </c>
       <c r="R37">
-        <v>42.7760208928122</v>
+        <v>42.77602089281221</v>
       </c>
       <c r="S37">
         <v>38.99275033978113</v>
@@ -56941,16 +56941,16 @@
         <v>69.29288653097682</v>
       </c>
       <c r="O39">
-        <v>47.61770917916451</v>
+        <v>47.6177091791645</v>
       </c>
       <c r="P39">
-        <v>52.48488723824204</v>
+        <v>52.48488723824203</v>
       </c>
       <c r="Q39">
-        <v>45.61017358285472</v>
+        <v>45.61017358285473</v>
       </c>
       <c r="R39">
-        <v>45.08562323165503</v>
+        <v>45.08562323165502</v>
       </c>
       <c r="S39">
         <v>41.73036205266747</v>
@@ -56993,7 +56993,7 @@
         <v>169.6889192175849</v>
       </c>
       <c r="L40">
-        <v>812.4814785386702</v>
+        <v>812.4814785386701</v>
       </c>
       <c r="M40">
         <v>30.83368056032016</v>
@@ -57063,10 +57063,10 @@
         <v>68.08412824485943</v>
       </c>
       <c r="O41">
-        <v>46.87346285273961</v>
+        <v>46.8734628527396</v>
       </c>
       <c r="P41">
-        <v>51.14941048568829</v>
+        <v>51.14941048568828</v>
       </c>
       <c r="Q41">
         <v>44.86690753985125</v>
@@ -57085,7 +57085,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>44.67554183229448</v>
+        <v>44.67554183229447</v>
       </c>
       <c r="C42">
         <v>32.79143197778071</v>
@@ -57121,10 +57121,10 @@
         <v>30.78159002737185</v>
       </c>
       <c r="N42">
-        <v>68.07362239402548</v>
+        <v>68.07362239402549</v>
       </c>
       <c r="O42">
-        <v>46.62634715995687</v>
+        <v>46.62634715995686</v>
       </c>
       <c r="P42">
         <v>49.91546276175398</v>
@@ -57167,7 +57167,7 @@
         <v>29.94440025816711</v>
       </c>
       <c r="I43">
-        <v>26.82204555815281</v>
+        <v>26.8220455581528</v>
       </c>
       <c r="J43">
         <v>69.10222619892748</v>
@@ -57185,7 +57185,7 @@
         <v>68.04481533757436</v>
       </c>
       <c r="O43">
-        <v>46.23031145322429</v>
+        <v>46.2303114532243</v>
       </c>
       <c r="P43">
         <v>47.48973016980636</v>
@@ -57194,7 +57194,7 @@
         <v>41.09797760939592</v>
       </c>
       <c r="R43">
-        <v>43.08191721609943</v>
+        <v>43.08191721609942</v>
       </c>
       <c r="S43">
         <v>40.05742285860359</v>
@@ -57210,7 +57210,7 @@
         <v>29.14268690125126</v>
       </c>
       <c r="C44">
-        <v>37.5286284186472</v>
+        <v>37.52862841864721</v>
       </c>
       <c r="D44">
         <v>71.36891749749131</v>
@@ -57219,7 +57219,7 @@
         <v>128.8365788332929</v>
       </c>
       <c r="F44">
-        <v>25.82599326238883</v>
+        <v>25.82599326238882</v>
       </c>
       <c r="G44">
         <v>59.41820754114016</v>
@@ -57231,7 +57231,7 @@
         <v>26.74933946955921</v>
       </c>
       <c r="J44">
-        <v>71.72072240572422</v>
+        <v>71.7207224057242</v>
       </c>
       <c r="K44">
         <v>192.7769011031019</v>
@@ -57283,7 +57283,7 @@
         <v>25.54642156323228</v>
       </c>
       <c r="G45">
-        <v>57.57973865693282</v>
+        <v>57.57973865693283</v>
       </c>
       <c r="H45">
         <v>30.38119467085092</v>
@@ -57301,22 +57301,22 @@
         <v>400.6238161149208</v>
       </c>
       <c r="M45">
-        <v>30.88881182508415</v>
+        <v>30.88881182508414</v>
       </c>
       <c r="N45">
         <v>68.59178438778021</v>
       </c>
       <c r="O45">
-        <v>46.03712138441699</v>
+        <v>46.037121384417</v>
       </c>
       <c r="P45">
         <v>46.48649540384698</v>
       </c>
       <c r="Q45">
-        <v>40.46602961514871</v>
+        <v>40.46602961514872</v>
       </c>
       <c r="R45">
-        <v>42.27708057548156</v>
+        <v>42.27708057548155</v>
       </c>
       <c r="S45">
         <v>39.35669546455201</v>
@@ -57329,16 +57329,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>30.02329322719287</v>
+        <v>30.02329322719288</v>
       </c>
       <c r="C46">
         <v>44.58310669613932</v>
       </c>
       <c r="D46">
-        <v>64.53704426112981</v>
+        <v>64.53704426112982</v>
       </c>
       <c r="E46">
-        <v>145.5315034189484</v>
+        <v>145.5315034189483</v>
       </c>
       <c r="F46">
         <v>24.99447393827089</v>
@@ -57353,19 +57353,19 @@
         <v>26.35007864786472</v>
       </c>
       <c r="J46">
-        <v>66.977703410394</v>
+        <v>66.97770341039401</v>
       </c>
       <c r="K46">
         <v>184.0927951719446</v>
       </c>
       <c r="L46">
-        <v>425.1064987739091</v>
+        <v>425.1064987739092</v>
       </c>
       <c r="M46">
         <v>30.87998932003457</v>
       </c>
       <c r="N46">
-        <v>69.16652016389283</v>
+        <v>69.16652016389284</v>
       </c>
       <c r="O46">
         <v>46.25556596485053</v>
@@ -57380,7 +57380,7 @@
         <v>41.74490041474279</v>
       </c>
       <c r="S46">
-        <v>38.8294450082703</v>
+        <v>38.82944500827031</v>
       </c>
     </row>
     <row r="47">
@@ -57454,7 +57454,7 @@
         <v>37.52915743105552</v>
       </c>
       <c r="C48">
-        <v>42.53491433241096</v>
+        <v>42.53491433241095</v>
       </c>
       <c r="D48">
         <v>62.36711902898896</v>
@@ -57475,7 +57475,7 @@
         <v>28.03068367930117</v>
       </c>
       <c r="J48">
-        <v>63.03088464143117</v>
+        <v>63.03088464143118</v>
       </c>
       <c r="K48">
         <v>178.4920439872265</v>
@@ -57490,10 +57490,10 @@
         <v>70.63212544831146</v>
       </c>
       <c r="O48">
-        <v>46.69742749863198</v>
+        <v>46.69742749863197</v>
       </c>
       <c r="P48">
-        <v>47.12158539940397</v>
+        <v>47.12158539940396</v>
       </c>
       <c r="Q48">
         <v>40.83796609678972</v>
@@ -57548,16 +57548,16 @@
         <v>30.662919821853</v>
       </c>
       <c r="N49">
-        <v>70.89050971817821</v>
+        <v>70.89050971817822</v>
       </c>
       <c r="O49">
-        <v>46.72742004612123</v>
+        <v>46.72742004612124</v>
       </c>
       <c r="P49">
         <v>47.02659516346936</v>
       </c>
       <c r="Q49">
-        <v>40.73122680495167</v>
+        <v>40.73122680495166</v>
       </c>
       <c r="R49">
         <v>41.32431754210339</v>
@@ -57576,10 +57576,10 @@
         <v>42.52558890802528</v>
       </c>
       <c r="C50">
-        <v>40.52955925393318</v>
+        <v>40.52955925393319</v>
       </c>
       <c r="D50">
-        <v>62.7101980977832</v>
+        <v>62.71019809778321</v>
       </c>
       <c r="E50">
         <v>167.5800866774468</v>
@@ -57588,7 +57588,7 @@
         <v>23.10277025467129</v>
       </c>
       <c r="G50">
-        <v>53.50983457766694</v>
+        <v>53.50983457766693</v>
       </c>
       <c r="H50">
         <v>31.50539775033668</v>
@@ -57603,7 +57603,7 @@
         <v>178.8893795726938</v>
       </c>
       <c r="L50">
-        <v>437.9703505374879</v>
+        <v>437.970350537488</v>
       </c>
       <c r="M50">
         <v>30.77122424943216</v>
@@ -57621,7 +57621,7 @@
         <v>41.60090365124211</v>
       </c>
       <c r="R50">
-        <v>41.47349478841883</v>
+        <v>41.47349478841881</v>
       </c>
       <c r="S50">
         <v>38.45641418546007</v>
@@ -57640,7 +57640,7 @@
         <v>42.89594845087503</v>
       </c>
       <c r="D51">
-        <v>61.70776571508301</v>
+        <v>61.707765715083</v>
       </c>
       <c r="E51">
         <v>179.2953815116693</v>
@@ -57658,13 +57658,13 @@
         <v>27.34639401871621</v>
       </c>
       <c r="J51">
-        <v>65.39911295314022</v>
+        <v>65.39911295314023</v>
       </c>
       <c r="K51">
         <v>191.980979707724</v>
       </c>
       <c r="L51">
-        <v>420.0576745626794</v>
+        <v>420.0576745626795</v>
       </c>
       <c r="M51">
         <v>30.92080149729796</v>
@@ -57673,13 +57673,13 @@
         <v>70.03031104824525</v>
       </c>
       <c r="O51">
-        <v>46.61036954168864</v>
+        <v>46.61036954168863</v>
       </c>
       <c r="P51">
-        <v>48.43387697433552</v>
+        <v>48.43387697433551</v>
       </c>
       <c r="Q51">
-        <v>42.53983066814297</v>
+        <v>42.53983066814298</v>
       </c>
       <c r="R51">
         <v>41.53247594247362</v>
@@ -57710,10 +57710,10 @@
         <v>23.81786326903725</v>
       </c>
       <c r="G52">
-        <v>53.29794983347808</v>
+        <v>53.29794983347807</v>
       </c>
       <c r="H52">
-        <v>31.42811861160269</v>
+        <v>31.42811861160268</v>
       </c>
       <c r="I52">
         <v>26.51642086664401</v>
@@ -57728,7 +57728,7 @@
         <v>416.5543796638958</v>
       </c>
       <c r="M52">
-        <v>31.41208023657974</v>
+        <v>31.41208023657975</v>
       </c>
       <c r="N52">
         <v>68.7540585903192</v>
@@ -57740,13 +57740,13 @@
         <v>48.59673543303903</v>
       </c>
       <c r="Q52">
-        <v>42.72555177829502</v>
+        <v>42.72555177829501</v>
       </c>
       <c r="R52">
-        <v>41.5670225779725</v>
+        <v>41.56702257797251</v>
       </c>
       <c r="S52">
-        <v>38.43321750668409</v>
+        <v>38.43321750668407</v>
       </c>
     </row>
     <row r="53">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>53.67141597202161</v>
+        <v>53.6714159720216</v>
       </c>
       <c r="C53">
         <v>49.90344910839888</v>
@@ -57777,7 +57777,7 @@
         <v>31.74216155829806</v>
       </c>
       <c r="I53">
-        <v>25.63742447826377</v>
+        <v>25.63742447826376</v>
       </c>
       <c r="J53">
         <v>67.26777338683063</v>
@@ -57795,7 +57795,7 @@
         <v>68.70734201700458</v>
       </c>
       <c r="O53">
-        <v>46.62615065727009</v>
+        <v>46.6261506572701</v>
       </c>
       <c r="P53">
         <v>48.79429031665723</v>
@@ -57835,7 +57835,7 @@
         <v>52.99904165410469</v>
       </c>
       <c r="H54">
-        <v>31.97035968134646</v>
+        <v>31.97035968134645</v>
       </c>
       <c r="I54">
         <v>24.88477657391408</v>
@@ -57844,7 +57844,7 @@
         <v>68.77897084596246</v>
       </c>
       <c r="K54">
-        <v>209.4371710899279</v>
+        <v>209.437171089928</v>
       </c>
       <c r="L54">
         <v>419.8794006181586</v>
@@ -57881,13 +57881,13 @@
         <v>49.31104615928612</v>
       </c>
       <c r="C55">
-        <v>68.63010098462225</v>
+        <v>68.63010098462226</v>
       </c>
       <c r="D55">
         <v>61.06520141304053</v>
       </c>
       <c r="E55">
-        <v>177.3848209134111</v>
+        <v>177.3848209134112</v>
       </c>
       <c r="F55">
         <v>25.43368111610894</v>
@@ -57896,10 +57896,10 @@
         <v>53.7414379664222</v>
       </c>
       <c r="H55">
-        <v>32.06272913683828</v>
+        <v>32.06272913683829</v>
       </c>
       <c r="I55">
-        <v>24.90749180759548</v>
+        <v>24.90749180759549</v>
       </c>
       <c r="J55">
         <v>69.83917465923025</v>
@@ -57917,7 +57917,7 @@
         <v>66.29851010062937</v>
       </c>
       <c r="O55">
-        <v>46.33283487303412</v>
+        <v>46.33283487303413</v>
       </c>
       <c r="P55">
         <v>48.23404569385816</v>
@@ -57939,13 +57939,13 @@
         </is>
       </c>
       <c r="B56">
-        <v>49.69536791897391</v>
+        <v>49.69536791897392</v>
       </c>
       <c r="C56">
         <v>72.56096550343561</v>
       </c>
       <c r="D56">
-        <v>61.37973370345304</v>
+        <v>61.37973370345305</v>
       </c>
       <c r="E56">
         <v>187.0602983105077</v>
@@ -57957,7 +57957,7 @@
         <v>54.18152832524548</v>
       </c>
       <c r="H56">
-        <v>32.28991973622067</v>
+        <v>32.28991973622068</v>
       </c>
       <c r="I56">
         <v>24.1887435365934</v>
@@ -58051,7 +58051,7 @@
         <v>41.96833457639875</v>
       </c>
       <c r="S57">
-        <v>38.84887921094194</v>
+        <v>38.84887921094195</v>
       </c>
     </row>
     <row r="58">
@@ -58202,10 +58202,10 @@
         <v>34.33408016055922</v>
       </c>
       <c r="D5">
-        <v>72.57270244042624</v>
+        <v>72.57270244042626</v>
       </c>
       <c r="E5">
-        <v>96.54321150500368</v>
+        <v>96.54321150500367</v>
       </c>
       <c r="F5">
         <v>27.91657095788006</v>
@@ -58247,7 +58247,7 @@
         <v>45.07047432720729</v>
       </c>
       <c r="S5">
-        <v>42.00813105415219</v>
+        <v>42.0081310541522</v>
       </c>
     </row>
     <row r="6">
@@ -58284,7 +58284,7 @@
         <v>82.42348445103019</v>
       </c>
       <c r="K6">
-        <v>211.3083374050534</v>
+        <v>211.3083374050533</v>
       </c>
       <c r="L6">
         <v>484.1099999444648</v>
@@ -58305,7 +58305,7 @@
         <v>42.75554181817363</v>
       </c>
       <c r="R6">
-        <v>45.53303715132483</v>
+        <v>45.53303715132484</v>
       </c>
       <c r="S6">
         <v>42.43626594394609</v>
@@ -58318,7 +58318,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>39.99688813820327</v>
+        <v>39.99688813820328</v>
       </c>
       <c r="C7">
         <v>32.80677523958084</v>
@@ -58336,13 +58336,13 @@
         <v>61.86834650537684</v>
       </c>
       <c r="H7">
-        <v>29.91749750488059</v>
+        <v>29.9174975048806</v>
       </c>
       <c r="I7">
         <v>29.51085329019049</v>
       </c>
       <c r="J7">
-        <v>82.78142245561214</v>
+        <v>82.78142245561216</v>
       </c>
       <c r="K7">
         <v>212.5992904804517</v>
@@ -58351,7 +58351,7 @@
         <v>443.7064821190849</v>
       </c>
       <c r="M7">
-        <v>34.22977343410949</v>
+        <v>34.22977343410948</v>
       </c>
       <c r="N7">
         <v>81.32084305098861</v>
@@ -58360,10 +58360,10 @@
         <v>49.7452810944588</v>
       </c>
       <c r="P7">
-        <v>51.09768039001748</v>
+        <v>51.09768039001747</v>
       </c>
       <c r="Q7">
-        <v>45.24941342598458</v>
+        <v>45.24941342598459</v>
       </c>
       <c r="R7">
         <v>46.20840765306679</v>
@@ -58379,10 +58379,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>39.88654215373177</v>
+        <v>39.88654215373176</v>
       </c>
       <c r="C8">
-        <v>34.85169826133713</v>
+        <v>34.85169826133714</v>
       </c>
       <c r="D8">
         <v>77.20023973980513</v>
@@ -58397,13 +58397,13 @@
         <v>63.08576988414811</v>
       </c>
       <c r="H8">
-        <v>29.91278148934233</v>
+        <v>29.91278148934234</v>
       </c>
       <c r="I8">
-        <v>29.85461865649065</v>
+        <v>29.85461865649066</v>
       </c>
       <c r="J8">
-        <v>85.09544089388305</v>
+        <v>85.09544089388304</v>
       </c>
       <c r="K8">
         <v>212.9303126121696</v>
@@ -58418,7 +58418,7 @@
         <v>80.38172621729919</v>
       </c>
       <c r="O8">
-        <v>49.6507855196357</v>
+        <v>49.65078551963571</v>
       </c>
       <c r="P8">
         <v>51.21312414623964</v>
@@ -58440,13 +58440,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>41.11128291889104</v>
+        <v>41.11128291889103</v>
       </c>
       <c r="C9">
         <v>35.39044682356686</v>
       </c>
       <c r="D9">
-        <v>77.90500650544668</v>
+        <v>77.90500650544666</v>
       </c>
       <c r="E9">
         <v>104.2861170014935</v>
@@ -58461,7 +58461,7 @@
         <v>29.64346610768968</v>
       </c>
       <c r="I9">
-        <v>30.73410956045029</v>
+        <v>30.7341095604503</v>
       </c>
       <c r="J9">
         <v>84.52845832178041</v>
@@ -58482,13 +58482,13 @@
         <v>49.31075595514006</v>
       </c>
       <c r="P9">
-        <v>51.21812140518736</v>
+        <v>51.21812140518737</v>
       </c>
       <c r="Q9">
         <v>45.73152957707125</v>
       </c>
       <c r="R9">
-        <v>46.54364517848526</v>
+        <v>46.54364517848525</v>
       </c>
       <c r="S9">
         <v>43.38319138097334</v>
@@ -58501,7 +58501,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>42.34616371851</v>
+        <v>42.34616371851001</v>
       </c>
       <c r="C10">
         <v>35.83463490635256</v>
@@ -58531,7 +58531,7 @@
         <v>223.3830306099368</v>
       </c>
       <c r="L10">
-        <v>424.7063014655495</v>
+        <v>424.7063014655494</v>
       </c>
       <c r="M10">
         <v>33.28518949537866</v>
@@ -58562,7 +58562,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>41.88526525377317</v>
+        <v>41.88526525377318</v>
       </c>
       <c r="C11">
         <v>43.90448503423455</v>
@@ -58592,7 +58592,7 @@
         <v>233.0826415967232</v>
       </c>
       <c r="L11">
-        <v>459.6633799196733</v>
+        <v>459.6633799196732</v>
       </c>
       <c r="M11">
         <v>32.51401717439407</v>
@@ -58604,7 +58604,7 @@
         <v>49.01475709740672</v>
       </c>
       <c r="P11">
-        <v>51.4104073535429</v>
+        <v>51.41040735354291</v>
       </c>
       <c r="Q11">
         <v>45.40427384938643</v>
@@ -58613,7 +58613,7 @@
         <v>45.98192894458971</v>
       </c>
       <c r="S11">
-        <v>42.75924662518535</v>
+        <v>42.75924662518533</v>
       </c>
     </row>
     <row r="12">
@@ -58623,7 +58623,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>43.56637337587393</v>
+        <v>43.56637337587392</v>
       </c>
       <c r="C12">
         <v>45.87450810162214</v>
@@ -58641,7 +58641,7 @@
         <v>63.2278762269488</v>
       </c>
       <c r="H12">
-        <v>29.96111636288327</v>
+        <v>29.96111636288328</v>
       </c>
       <c r="I12">
         <v>33.14882892935418</v>
@@ -58714,19 +58714,19 @@
         <v>234.8123535903316</v>
       </c>
       <c r="L13">
-        <v>498.9659996197885</v>
+        <v>498.9659996197884</v>
       </c>
       <c r="M13">
         <v>31.82557122579656</v>
       </c>
       <c r="N13">
-        <v>82.768755455262</v>
+        <v>82.76875545526198</v>
       </c>
       <c r="O13">
-        <v>49.22264041864339</v>
+        <v>49.22264041864338</v>
       </c>
       <c r="P13">
-        <v>51.51237110979768</v>
+        <v>51.51237110979767</v>
       </c>
       <c r="Q13">
         <v>45.42378728836479</v>
@@ -58751,7 +58751,7 @@
         <v>43.58307530850774</v>
       </c>
       <c r="D14">
-        <v>74.34885287498898</v>
+        <v>74.34885287498899</v>
       </c>
       <c r="E14">
         <v>117.4099745473893</v>
@@ -58778,16 +58778,16 @@
         <v>499.7004158819794</v>
       </c>
       <c r="M14">
-        <v>31.33282568183331</v>
+        <v>31.3328256818333</v>
       </c>
       <c r="N14">
-        <v>82.03317834640931</v>
+        <v>82.03317834640933</v>
       </c>
       <c r="O14">
         <v>48.72770639993925</v>
       </c>
       <c r="P14">
-        <v>51.01209250820325</v>
+        <v>51.01209250820326</v>
       </c>
       <c r="Q14">
         <v>44.90611817063149</v>
@@ -58827,16 +58827,16 @@
         <v>29.6381902290312</v>
       </c>
       <c r="I15">
-        <v>32.69238034679101</v>
+        <v>32.692380346791</v>
       </c>
       <c r="J15">
-        <v>72.92249318063571</v>
+        <v>72.92249318063573</v>
       </c>
       <c r="K15">
         <v>223.4893799016372</v>
       </c>
       <c r="L15">
-        <v>477.250340963259</v>
+        <v>477.2503409632589</v>
       </c>
       <c r="M15">
         <v>31.27765295372554</v>
@@ -58848,7 +58848,7 @@
         <v>48.22552231745238</v>
       </c>
       <c r="P15">
-        <v>50.84109858054463</v>
+        <v>50.84109858054462</v>
       </c>
       <c r="Q15">
         <v>44.87092650786747</v>
@@ -58857,7 +58857,7 @@
         <v>44.36944481056047</v>
       </c>
       <c r="S15">
-        <v>41.1897522952582</v>
+        <v>41.18975229525821</v>
       </c>
     </row>
     <row r="16">
@@ -58885,10 +58885,10 @@
         <v>60.0521055448629</v>
       </c>
       <c r="H16">
-        <v>28.64442662284738</v>
+        <v>28.64442662284737</v>
       </c>
       <c r="I16">
-        <v>32.14548825495756</v>
+        <v>32.14548825495757</v>
       </c>
       <c r="J16">
         <v>70.13425835374827</v>
@@ -58903,7 +58903,7 @@
         <v>31.31706572623744</v>
       </c>
       <c r="N16">
-        <v>81.55043383824926</v>
+        <v>81.55043383824928</v>
       </c>
       <c r="O16">
         <v>47.85009884270436</v>
@@ -58931,7 +58931,7 @@
         <v>48.60300349772562</v>
       </c>
       <c r="C17">
-        <v>31.67294779330799</v>
+        <v>31.67294779330798</v>
       </c>
       <c r="D17">
         <v>68.9448435668875</v>
@@ -58955,22 +58955,22 @@
         <v>65.73621719238696</v>
       </c>
       <c r="K17">
-        <v>227.9924105279671</v>
+        <v>227.992410527967</v>
       </c>
       <c r="L17">
-        <v>537.2547219988764</v>
+        <v>537.2547219988766</v>
       </c>
       <c r="M17">
         <v>31.16338573704774</v>
       </c>
       <c r="N17">
-        <v>80.34694373004712</v>
+        <v>80.34694373004713</v>
       </c>
       <c r="O17">
         <v>47.14304258578183</v>
       </c>
       <c r="P17">
-        <v>49.73925140566323</v>
+        <v>49.73925140566322</v>
       </c>
       <c r="Q17">
         <v>43.34015202803718</v>
@@ -58979,7 +58979,7 @@
         <v>42.51737646278772</v>
       </c>
       <c r="S17">
-        <v>39.31185000952479</v>
+        <v>39.3118500095248</v>
       </c>
     </row>
     <row r="18">
@@ -58989,7 +58989,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>47.13696396002527</v>
+        <v>47.13696396002528</v>
       </c>
       <c r="C18">
         <v>30.83395403531721</v>
@@ -59004,7 +59004,7 @@
         <v>27.062453418683</v>
       </c>
       <c r="G18">
-        <v>57.33099344674521</v>
+        <v>57.33099344674522</v>
       </c>
       <c r="H18">
         <v>27.46211950239073</v>
@@ -59034,13 +59034,13 @@
         <v>49.36145879474552</v>
       </c>
       <c r="Q18">
-        <v>42.90758430232226</v>
+        <v>42.90758430232225</v>
       </c>
       <c r="R18">
         <v>42.23753611074426</v>
       </c>
       <c r="S18">
-        <v>39.02200670546313</v>
+        <v>39.02200670546312</v>
       </c>
     </row>
     <row r="19">
@@ -59056,10 +59056,10 @@
         <v>31.50227782669144</v>
       </c>
       <c r="D19">
-        <v>67.43017184197585</v>
+        <v>67.43017184197586</v>
       </c>
       <c r="E19">
-        <v>98.72316295997383</v>
+        <v>98.72316295997382</v>
       </c>
       <c r="F19">
         <v>25.98721789932765</v>
@@ -59083,7 +59083,7 @@
         <v>601.6345406876668</v>
       </c>
       <c r="M19">
-        <v>31.35908633509521</v>
+        <v>31.35908633509522</v>
       </c>
       <c r="N19">
         <v>78.50223503410751</v>
@@ -59098,7 +59098,7 @@
         <v>42.78691736598478</v>
       </c>
       <c r="R19">
-        <v>42.01576847158864</v>
+        <v>42.01576847158865</v>
       </c>
       <c r="S19">
         <v>38.82332821351395</v>
@@ -59111,7 +59111,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>46.71188681767406</v>
+        <v>46.71188681767405</v>
       </c>
       <c r="C20">
         <v>30.03281369535166</v>
@@ -59138,7 +59138,7 @@
         <v>74.75182301218499</v>
       </c>
       <c r="K20">
-        <v>215.6817528146144</v>
+        <v>215.6817528146143</v>
       </c>
       <c r="L20">
         <v>583.5349137788235</v>
@@ -59147,7 +59147,7 @@
         <v>31.30994323970241</v>
       </c>
       <c r="N20">
-        <v>77.5410304788014</v>
+        <v>77.54103047880142</v>
       </c>
       <c r="O20">
         <v>47.07914049197536</v>
@@ -59159,10 +59159,10 @@
         <v>42.51467468535887</v>
       </c>
       <c r="R20">
-        <v>41.82607093314867</v>
+        <v>41.82607093314866</v>
       </c>
       <c r="S20">
-        <v>38.66544176044728</v>
+        <v>38.66544176044727</v>
       </c>
     </row>
     <row r="21">
@@ -59172,13 +59172,13 @@
         </is>
       </c>
       <c r="B21">
-        <v>46.18917147425603</v>
+        <v>46.18917147425602</v>
       </c>
       <c r="C21">
         <v>33.11970894710917</v>
       </c>
       <c r="D21">
-        <v>68.05316630897542</v>
+        <v>68.05316630897543</v>
       </c>
       <c r="E21">
         <v>108.39762916426</v>
@@ -59190,7 +59190,7 @@
         <v>56.12041216344489</v>
       </c>
       <c r="H21">
-        <v>27.67315391068013</v>
+        <v>27.67315391068014</v>
       </c>
       <c r="I21">
         <v>30.55767491805589</v>
@@ -59220,7 +59220,7 @@
         <v>42.67881318562876</v>
       </c>
       <c r="R21">
-        <v>42.08967582922407</v>
+        <v>42.08967582922408</v>
       </c>
       <c r="S21">
         <v>38.9653960502844</v>
@@ -59233,7 +59233,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>49.99414470901727</v>
+        <v>49.99414470901726</v>
       </c>
       <c r="C22">
         <v>36.00314526977149</v>
@@ -59251,13 +59251,13 @@
         <v>56.70930984598689</v>
       </c>
       <c r="H22">
-        <v>27.61520467865636</v>
+        <v>27.61520467865635</v>
       </c>
       <c r="I22">
         <v>31.19811782208997</v>
       </c>
       <c r="J22">
-        <v>80.00324748881295</v>
+        <v>80.00324748881296</v>
       </c>
       <c r="K22">
         <v>203.3356367609516</v>
@@ -59281,7 +59281,7 @@
         <v>43.23435355244958</v>
       </c>
       <c r="R22">
-        <v>42.11386499632063</v>
+        <v>42.11386499632062</v>
       </c>
       <c r="S22">
         <v>39.00519174705249</v>
@@ -59318,7 +59318,7 @@
         <v>30.53477740575802</v>
       </c>
       <c r="J23">
-        <v>82.93258675138385</v>
+        <v>82.93258675138387</v>
       </c>
       <c r="K23">
         <v>211.3142726691892</v>
@@ -59330,16 +59330,16 @@
         <v>30.77077362693317</v>
       </c>
       <c r="N23">
-        <v>80.69394592307442</v>
+        <v>80.69394592307441</v>
       </c>
       <c r="O23">
-        <v>47.29653997801208</v>
+        <v>47.29653997801209</v>
       </c>
       <c r="P23">
-        <v>50.48244914561144</v>
+        <v>50.48244914561143</v>
       </c>
       <c r="Q23">
-        <v>43.90039225676322</v>
+        <v>43.90039225676323</v>
       </c>
       <c r="R23">
         <v>42.42688169872611</v>
@@ -59358,13 +59358,13 @@
         <v>52.79436574486343</v>
       </c>
       <c r="C24">
-        <v>38.56726981747022</v>
+        <v>38.56726981747023</v>
       </c>
       <c r="D24">
-        <v>70.54452122339556</v>
+        <v>70.54452122339555</v>
       </c>
       <c r="E24">
-        <v>98.042780524536</v>
+        <v>98.04278052453598</v>
       </c>
       <c r="F24">
         <v>25.60453446182218</v>
@@ -59403,7 +59403,7 @@
         <v>43.95025605472809</v>
       </c>
       <c r="R24">
-        <v>42.48847354967535</v>
+        <v>42.48847354967536</v>
       </c>
       <c r="S24">
         <v>39.31397081447813</v>
@@ -59437,7 +59437,7 @@
         <v>28.92871357738754</v>
       </c>
       <c r="I25">
-        <v>29.31428090505189</v>
+        <v>29.31428090505188</v>
       </c>
       <c r="J25">
         <v>83.81007609814007</v>
@@ -59452,13 +59452,13 @@
         <v>30.64785898707454</v>
       </c>
       <c r="N25">
-        <v>80.64509857614162</v>
+        <v>80.64509857614161</v>
       </c>
       <c r="O25">
         <v>47.68029548193154</v>
       </c>
       <c r="P25">
-        <v>50.77521271796018</v>
+        <v>50.77521271796019</v>
       </c>
       <c r="Q25">
         <v>44.24459885549019</v>
@@ -59483,7 +59483,7 @@
         <v>31.75865342313341</v>
       </c>
       <c r="D26">
-        <v>71.7315887329884</v>
+        <v>71.73158873298841</v>
       </c>
       <c r="E26">
         <v>91.88551004163226</v>
@@ -59492,7 +59492,7 @@
         <v>25.63494883873802</v>
       </c>
       <c r="G26">
-        <v>58.75991790027334</v>
+        <v>58.75991790027333</v>
       </c>
       <c r="H26">
         <v>29.51956864223228</v>
@@ -59501,7 +59501,7 @@
         <v>29.07867655391956</v>
       </c>
       <c r="J26">
-        <v>83.86189673584354</v>
+        <v>83.86189673584353</v>
       </c>
       <c r="K26">
         <v>238.0251219481412</v>
@@ -59519,7 +59519,7 @@
         <v>48.21585779495103</v>
       </c>
       <c r="P26">
-        <v>51.03373434707803</v>
+        <v>51.03373434707804</v>
       </c>
       <c r="Q26">
         <v>44.41608123850283</v>
@@ -59538,10 +59538,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>51.17294242373447</v>
+        <v>51.17294242373448</v>
       </c>
       <c r="C27">
-        <v>31.58683891721537</v>
+        <v>31.58683891721538</v>
       </c>
       <c r="D27">
         <v>70.16377707179828</v>
@@ -59571,7 +59571,7 @@
         <v>533.084995009336</v>
       </c>
       <c r="M27">
-        <v>31.3975931659399</v>
+        <v>31.39759316593991</v>
       </c>
       <c r="N27">
         <v>79.86040393994294</v>
@@ -59580,7 +59580,7 @@
         <v>48.58988700469624</v>
       </c>
       <c r="P27">
-        <v>50.52528835229223</v>
+        <v>50.52528835229224</v>
       </c>
       <c r="Q27">
         <v>44.16030903800108</v>
@@ -59608,7 +59608,7 @@
         <v>72.12087484154561</v>
       </c>
       <c r="E28">
-        <v>90.31959149005414</v>
+        <v>90.31959149005412</v>
       </c>
       <c r="F28">
         <v>24.51640808669082</v>
@@ -59629,7 +59629,7 @@
         <v>252.0098622646383</v>
       </c>
       <c r="L28">
-        <v>555.0977214516854</v>
+        <v>555.0977214516855</v>
       </c>
       <c r="M28">
         <v>31.80005614712871</v>
@@ -59660,13 +59660,13 @@
         </is>
       </c>
       <c r="B29">
-        <v>52.53599551463439</v>
+        <v>52.5359955146344</v>
       </c>
       <c r="C29">
         <v>39.78208855893607</v>
       </c>
       <c r="D29">
-        <v>73.57052798137664</v>
+        <v>73.57052798137663</v>
       </c>
       <c r="E29">
         <v>93.5222264899506</v>
@@ -59690,13 +59690,13 @@
         <v>264.3333097234497</v>
       </c>
       <c r="L29">
-        <v>526.5373112044044</v>
+        <v>526.5373112044045</v>
       </c>
       <c r="M29">
         <v>31.65439414858982</v>
       </c>
       <c r="N29">
-        <v>78.54849846306917</v>
+        <v>78.54849846306915</v>
       </c>
       <c r="O29">
         <v>49.12973019176946</v>
@@ -59708,7 +59708,7 @@
         <v>45.33991398095884</v>
       </c>
       <c r="R29">
-        <v>44.2316153973011</v>
+        <v>44.23161539730111</v>
       </c>
       <c r="S29">
         <v>40.72770652508238</v>
@@ -59736,7 +59736,7 @@
         <v>24.01365453007747</v>
       </c>
       <c r="G30">
-        <v>59.81106784405815</v>
+        <v>59.81106784405817</v>
       </c>
       <c r="H30">
         <v>31.18484644864297</v>
@@ -59754,7 +59754,7 @@
         <v>513.6026612126184</v>
       </c>
       <c r="M30">
-        <v>31.17628854270774</v>
+        <v>31.17628854270773</v>
       </c>
       <c r="N30">
         <v>77.68687162282595</v>
@@ -59788,7 +59788,7 @@
         <v>47.44011142930895</v>
       </c>
       <c r="D31">
-        <v>76.38191377238208</v>
+        <v>76.38191377238209</v>
       </c>
       <c r="E31">
         <v>100.7108749522066</v>
@@ -59818,13 +59818,13 @@
         <v>30.81207886958216</v>
       </c>
       <c r="N31">
-        <v>76.20012794288694</v>
+        <v>76.20012794288695</v>
       </c>
       <c r="O31">
-        <v>48.39928138557745</v>
+        <v>48.39928138557746</v>
       </c>
       <c r="P31">
-        <v>51.95224584012494</v>
+        <v>51.95224584012493</v>
       </c>
       <c r="Q31">
         <v>45.4781535872868</v>
@@ -59882,7 +59882,7 @@
         <v>74.84685329481279</v>
       </c>
       <c r="O32">
-        <v>47.71258154963953</v>
+        <v>47.71258154963952</v>
       </c>
       <c r="P32">
         <v>51.27715890986079</v>
@@ -59949,7 +59949,7 @@
         <v>50.87652045351876</v>
       </c>
       <c r="Q33">
-        <v>44.56785240169803</v>
+        <v>44.56785240169805</v>
       </c>
       <c r="R33">
         <v>43.18341599199069</v>
@@ -59968,7 +59968,7 @@
         <v>53.21096571205766</v>
       </c>
       <c r="C34">
-        <v>36.33297222472299</v>
+        <v>36.332972224723</v>
       </c>
       <c r="D34">
         <v>73.42255310784105</v>
@@ -59980,22 +59980,22 @@
         <v>24.28149864734726</v>
       </c>
       <c r="G34">
-        <v>59.94492990584525</v>
+        <v>59.94492990584524</v>
       </c>
       <c r="H34">
         <v>30.38727614367219</v>
       </c>
       <c r="I34">
-        <v>25.76451654722264</v>
+        <v>25.76451654722265</v>
       </c>
       <c r="J34">
-        <v>64.97801355441784</v>
+        <v>64.97801355441786</v>
       </c>
       <c r="K34">
         <v>304.8649074799448</v>
       </c>
       <c r="L34">
-        <v>607.8504933498252</v>
+        <v>607.8504933498253</v>
       </c>
       <c r="M34">
         <v>30.88798684975019</v>
@@ -60013,10 +60013,10 @@
         <v>44.7523267597162</v>
       </c>
       <c r="R34">
-        <v>43.48696964154593</v>
+        <v>43.48696964154595</v>
       </c>
       <c r="S34">
-        <v>39.78530668254342</v>
+        <v>39.78530668254341</v>
       </c>
     </row>
     <row r="35">
@@ -60041,7 +60041,7 @@
         <v>25.61856961143787</v>
       </c>
       <c r="G35">
-        <v>60.91944907603672</v>
+        <v>60.91944907603671</v>
       </c>
       <c r="H35">
         <v>31.60527393597978</v>
@@ -60059,7 +60059,7 @@
         <v>661.7559925486061</v>
       </c>
       <c r="M35">
-        <v>31.70222575050424</v>
+        <v>31.70222575050425</v>
       </c>
       <c r="N35">
         <v>76.74117677414954</v>
@@ -60111,7 +60111,7 @@
         <v>26.50906840253041</v>
       </c>
       <c r="J36">
-        <v>66.5195688868976</v>
+        <v>66.51956888689762</v>
       </c>
       <c r="K36">
         <v>309.0378214710937</v>
@@ -60123,7 +60123,7 @@
         <v>32.66455627098728</v>
       </c>
       <c r="N36">
-        <v>78.81068936121254</v>
+        <v>78.81068936121252</v>
       </c>
       <c r="O36">
         <v>51.83346154098597</v>
@@ -60138,7 +60138,7 @@
         <v>46.68025449627854</v>
       </c>
       <c r="S36">
-        <v>42.43167225565778</v>
+        <v>42.43167225565777</v>
       </c>
     </row>
     <row r="37">
@@ -60160,7 +60160,7 @@
         <v>124.3098489757331</v>
       </c>
       <c r="F37">
-        <v>28.39890835755476</v>
+        <v>28.39890835755475</v>
       </c>
       <c r="G37">
         <v>67.86207329288055</v>
@@ -60227,7 +60227,7 @@
         <v>70.86165817900419</v>
       </c>
       <c r="H38">
-        <v>33.56031293674343</v>
+        <v>33.56031293674344</v>
       </c>
       <c r="I38">
         <v>28.25031026280228</v>
@@ -60245,7 +60245,7 @@
         <v>33.4981149811943</v>
       </c>
       <c r="N38">
-        <v>78.61910433101491</v>
+        <v>78.61910433101492</v>
       </c>
       <c r="O38">
         <v>52.70580889568023</v>
@@ -60257,7 +60257,7 @@
         <v>47.21134581232239</v>
       </c>
       <c r="R38">
-        <v>48.95239323845906</v>
+        <v>48.95239323845907</v>
       </c>
       <c r="S38">
         <v>44.93255586235711</v>
@@ -60276,7 +60276,7 @@
         <v>51.83573251010246</v>
       </c>
       <c r="D39">
-        <v>87.34592766010152</v>
+        <v>87.34592766010151</v>
       </c>
       <c r="E39">
         <v>116.3083659310512</v>
@@ -60294,7 +60294,7 @@
         <v>28.77676932440333</v>
       </c>
       <c r="J39">
-        <v>62.42020689271629</v>
+        <v>62.42020689271631</v>
       </c>
       <c r="K39">
         <v>183.5669038097261</v>
@@ -60346,7 +60346,7 @@
         <v>29.11130721843034</v>
       </c>
       <c r="G40">
-        <v>69.68044140956718</v>
+        <v>69.68044140956719</v>
       </c>
       <c r="H40">
         <v>31.01229204481102</v>
@@ -60361,13 +60361,13 @@
         <v>176.3744502477292</v>
       </c>
       <c r="L40">
-        <v>839.4344004215063</v>
+        <v>839.4344004215064</v>
       </c>
       <c r="M40">
-        <v>32.66891993466036</v>
+        <v>32.66891993466037</v>
       </c>
       <c r="N40">
-        <v>72.9825447112641</v>
+        <v>72.98254471126413</v>
       </c>
       <c r="O40">
         <v>49.38302990604838</v>
@@ -60398,7 +60398,7 @@
         <v>34.85027409752195</v>
       </c>
       <c r="D41">
-        <v>83.22299079368987</v>
+        <v>83.22299079368986</v>
       </c>
       <c r="E41">
         <v>119.0172830445358</v>
@@ -60431,7 +60431,7 @@
         <v>71.68139484446134</v>
       </c>
       <c r="O41">
-        <v>48.86467216255249</v>
+        <v>48.8646721625525</v>
       </c>
       <c r="P41">
         <v>53.3248665497764</v>
@@ -60440,7 +60440,7 @@
         <v>46.72714566263269</v>
       </c>
       <c r="R41">
-        <v>46.03358185799926</v>
+        <v>46.03358185799927</v>
       </c>
       <c r="S41">
         <v>42.83179079445487</v>
@@ -60468,7 +60468,7 @@
         <v>27.58448026259628</v>
       </c>
       <c r="G42">
-        <v>65.37790867018111</v>
+        <v>65.3779086701811</v>
       </c>
       <c r="H42">
         <v>30.68043192402165</v>
@@ -60501,10 +60501,10 @@
         <v>45.57054293152824</v>
       </c>
       <c r="R42">
-        <v>45.4634533401332</v>
+        <v>45.46345334013319</v>
       </c>
       <c r="S42">
-        <v>42.28253792083373</v>
+        <v>42.28253792083374</v>
       </c>
     </row>
     <row r="43">
@@ -60532,7 +60532,7 @@
         <v>64.00018393808055</v>
       </c>
       <c r="H43">
-        <v>30.94261546768173</v>
+        <v>30.94261546768174</v>
       </c>
       <c r="I43">
         <v>28.23693319622026</v>
@@ -60547,22 +60547,22 @@
         <v>501.3946097470879</v>
       </c>
       <c r="M43">
-        <v>31.82350138367627</v>
+        <v>31.82350138367628</v>
       </c>
       <c r="N43">
         <v>71.86368338455918</v>
       </c>
       <c r="O43">
-        <v>48.14213791535747</v>
+        <v>48.14213791535746</v>
       </c>
       <c r="P43">
         <v>49.54117029734363</v>
       </c>
       <c r="Q43">
-        <v>42.81830799035957</v>
+        <v>42.81830799035956</v>
       </c>
       <c r="R43">
-        <v>44.87546893328398</v>
+        <v>44.87546893328397</v>
       </c>
       <c r="S43">
         <v>41.72524371483141</v>
@@ -60581,7 +60581,7 @@
         <v>38.11897011680451</v>
       </c>
       <c r="D44">
-        <v>74.40904667438805</v>
+        <v>74.40904667438807</v>
       </c>
       <c r="E44">
         <v>137.4100463377191</v>
@@ -60590,7 +60590,7 @@
         <v>27.42501046520139</v>
       </c>
       <c r="G44">
-        <v>62.31120282296699</v>
+        <v>62.31120282296698</v>
       </c>
       <c r="H44">
         <v>31.45362962833526</v>
@@ -60611,7 +60611,7 @@
         <v>31.68023477694915</v>
       </c>
       <c r="N44">
-        <v>72.80356896801217</v>
+        <v>72.80356896801219</v>
       </c>
       <c r="O44">
         <v>48.09276200755282</v>
@@ -60620,7 +60620,7 @@
         <v>49.04711340888603</v>
       </c>
       <c r="Q44">
-        <v>42.52706357666118</v>
+        <v>42.52706357666119</v>
       </c>
       <c r="R44">
         <v>44.51521936266398</v>
@@ -60669,10 +60669,10 @@
         <v>416.3390012305266</v>
       </c>
       <c r="M45">
-        <v>32.19082557067514</v>
+        <v>32.19082557067513</v>
       </c>
       <c r="N45">
-        <v>73.17908280935536</v>
+        <v>73.17908280935535</v>
       </c>
       <c r="O45">
         <v>48.11263051678154</v>
@@ -60684,7 +60684,7 @@
         <v>42.31487688695111</v>
       </c>
       <c r="R45">
-        <v>44.21776714511745</v>
+        <v>44.21776714511746</v>
       </c>
       <c r="S45">
         <v>41.1617054856308</v>
@@ -60712,7 +60712,7 @@
         <v>26.37905250124427</v>
       </c>
       <c r="G46">
-        <v>58.15478247490205</v>
+        <v>58.15478247490204</v>
       </c>
       <c r="H46">
         <v>31.97178259979898</v>
@@ -60721,7 +60721,7 @@
         <v>27.56524115420464</v>
       </c>
       <c r="J46">
-        <v>69.79021200246571</v>
+        <v>69.79021200246572</v>
       </c>
       <c r="K46">
         <v>191.1885775681703</v>
@@ -60733,10 +60733,10 @@
         <v>32.14292095863426</v>
       </c>
       <c r="N46">
-        <v>73.90088016062793</v>
+        <v>73.90088016062795</v>
       </c>
       <c r="O46">
-        <v>48.2471444647512</v>
+        <v>48.24714446475121</v>
       </c>
       <c r="P46">
         <v>48.39946049235665</v>
@@ -60794,10 +60794,10 @@
         <v>32.2286406237662</v>
       </c>
       <c r="N47">
-        <v>74.8456593444366</v>
+        <v>74.84565934443658</v>
       </c>
       <c r="O47">
-        <v>48.47521482099701</v>
+        <v>48.475214820997</v>
       </c>
       <c r="P47">
         <v>49.0657389096349</v>
@@ -60806,7 +60806,7 @@
         <v>42.46942991775482</v>
       </c>
       <c r="R47">
-        <v>43.13244007362121</v>
+        <v>43.13244007362123</v>
       </c>
       <c r="S47">
         <v>40.06995755807001</v>
@@ -60840,7 +60840,7 @@
         <v>32.47757401220348</v>
       </c>
       <c r="I48">
-        <v>29.26094902843149</v>
+        <v>29.2609490284315</v>
       </c>
       <c r="J48">
         <v>65.48355870665321</v>
@@ -60852,7 +60852,7 @@
         <v>477.7310973300599</v>
       </c>
       <c r="M48">
-        <v>32.17143179735235</v>
+        <v>32.17143179735234</v>
       </c>
       <c r="N48">
         <v>75.62451847500489</v>
@@ -60883,7 +60883,7 @@
         <v>38.46375682705511</v>
       </c>
       <c r="C49">
-        <v>39.85222781182706</v>
+        <v>39.85222781182705</v>
       </c>
       <c r="D49">
         <v>65.80513947393342</v>
@@ -60956,10 +60956,10 @@
         <v>24.69933633180106</v>
       </c>
       <c r="G50">
-        <v>57.19490171789758</v>
+        <v>57.19490171789757</v>
       </c>
       <c r="H50">
-        <v>32.67766119515908</v>
+        <v>32.67766119515907</v>
       </c>
       <c r="I50">
         <v>29.35913051256241</v>
@@ -60974,7 +60974,7 @@
         <v>457.1647644254889</v>
       </c>
       <c r="M50">
-        <v>32.4241742842795</v>
+        <v>32.42417428427949</v>
       </c>
       <c r="N50">
         <v>76.68279627397229</v>
@@ -60989,10 +60989,10 @@
         <v>43.81583478217694</v>
       </c>
       <c r="R50">
-        <v>43.65275529803963</v>
+        <v>43.65275529803962</v>
       </c>
       <c r="S50">
-        <v>40.48971353026876</v>
+        <v>40.48971353026875</v>
       </c>
     </row>
     <row r="51">
@@ -61020,7 +61020,7 @@
         <v>57.57638284040529</v>
       </c>
       <c r="H51">
-        <v>32.87027538774714</v>
+        <v>32.87027538774713</v>
       </c>
       <c r="I51">
         <v>28.52473843349957</v>
@@ -61032,7 +61032,7 @@
         <v>198.4823391486673</v>
       </c>
       <c r="L51">
-        <v>441.7268725562865</v>
+        <v>441.7268725562864</v>
       </c>
       <c r="M51">
         <v>32.80886571577701</v>
@@ -61041,10 +61041,10 @@
         <v>75.98403505569421</v>
       </c>
       <c r="O51">
-        <v>49.18862859048515</v>
+        <v>49.18862859048516</v>
       </c>
       <c r="P51">
-        <v>51.44081388695343</v>
+        <v>51.44081388695344</v>
       </c>
       <c r="Q51">
         <v>45.08476089347538</v>
@@ -61063,13 +61063,13 @@
         </is>
       </c>
       <c r="B52">
-        <v>55.3976858732363</v>
+        <v>55.39768587323631</v>
       </c>
       <c r="C52">
         <v>51.3226490393106</v>
       </c>
       <c r="D52">
-        <v>65.35625181925532</v>
+        <v>65.35625181925533</v>
       </c>
       <c r="E52">
         <v>194.7696016250992</v>
@@ -61078,13 +61078,13 @@
         <v>25.50966341291921</v>
       </c>
       <c r="G52">
-        <v>56.95962267150567</v>
+        <v>56.95962267150566</v>
       </c>
       <c r="H52">
         <v>32.59113690730952</v>
       </c>
       <c r="I52">
-        <v>27.62909805798809</v>
+        <v>27.62909805798808</v>
       </c>
       <c r="J52">
         <v>69.88540747133916</v>
@@ -61108,7 +61108,7 @@
         <v>51.42854542968662</v>
       </c>
       <c r="Q52">
-        <v>45.12252539154423</v>
+        <v>45.12252539154422</v>
       </c>
       <c r="R52">
         <v>43.82080168837069</v>
@@ -61148,7 +61148,7 @@
         <v>26.78740802652724</v>
       </c>
       <c r="J53">
-        <v>69.36930328520239</v>
+        <v>69.36930328520238</v>
       </c>
       <c r="K53">
         <v>223.2249220063151</v>
@@ -61169,7 +61169,7 @@
         <v>51.43458905674724</v>
       </c>
       <c r="Q53">
-        <v>45.16022846534706</v>
+        <v>45.16022846534705</v>
       </c>
       <c r="R53">
         <v>43.68080265916278</v>
@@ -61188,19 +61188,19 @@
         <v>59.26499414240893</v>
       </c>
       <c r="C54">
-        <v>61.81509267929689</v>
+        <v>61.8150926792969</v>
       </c>
       <c r="D54">
-        <v>63.69710650457925</v>
+        <v>63.69710650457926</v>
       </c>
       <c r="E54">
         <v>178.7287331046021</v>
       </c>
       <c r="F54">
-        <v>26.58975744978438</v>
+        <v>26.58975744978439</v>
       </c>
       <c r="G54">
-        <v>56.09930964145461</v>
+        <v>56.09930964145462</v>
       </c>
       <c r="H54">
         <v>33.02604870429732</v>
@@ -61224,7 +61224,7 @@
         <v>71.60983120376073</v>
       </c>
       <c r="O54">
-        <v>48.67562887472065</v>
+        <v>48.67562887472064</v>
       </c>
       <c r="P54">
         <v>51.38438806541829</v>
@@ -61270,7 +61270,7 @@
         <v>26.17160510725785</v>
       </c>
       <c r="J55">
-        <v>72.86585339982304</v>
+        <v>72.86585339982302</v>
       </c>
       <c r="K55">
         <v>205.2448286385165</v>
@@ -61282,19 +61282,19 @@
         <v>32.90509256712154</v>
       </c>
       <c r="N55">
-        <v>70.22137665643363</v>
+        <v>70.22137665643365</v>
       </c>
       <c r="O55">
         <v>48.26192566358799</v>
       </c>
       <c r="P55">
-        <v>50.32947007678575</v>
+        <v>50.32947007678576</v>
       </c>
       <c r="Q55">
-        <v>44.32599916442216</v>
+        <v>44.32599916442215</v>
       </c>
       <c r="R55">
-        <v>43.47432340746818</v>
+        <v>43.47432340746819</v>
       </c>
       <c r="S55">
         <v>40.16923319619236</v>
@@ -61310,7 +61310,7 @@
         <v>51.64147117147734</v>
       </c>
       <c r="C56">
-        <v>79.3848400545084</v>
+        <v>79.38484005450839</v>
       </c>
       <c r="D56">
         <v>64.09654798597198</v>
@@ -61319,7 +61319,7 @@
         <v>192.2713269103524</v>
       </c>
       <c r="F56">
-        <v>27.04615870662955</v>
+        <v>27.04615870662956</v>
       </c>
       <c r="G56">
         <v>56.75475094398856</v>
@@ -61331,7 +61331,7 @@
         <v>25.27119610033005</v>
       </c>
       <c r="J56">
-        <v>72.90079502885358</v>
+        <v>72.90079502885357</v>
       </c>
       <c r="K56">
         <v>189.2476262792248</v>
@@ -61343,7 +61343,7 @@
         <v>33.01556241911358</v>
       </c>
       <c r="N56">
-        <v>69.97868471234558</v>
+        <v>69.97868471234557</v>
       </c>
       <c r="O56">
         <v>48.21025566570817</v>
@@ -61371,13 +61371,13 @@
         <v>53.40578741181928</v>
       </c>
       <c r="C57">
-        <v>97.67415363230546</v>
+        <v>97.67415363230548</v>
       </c>
       <c r="D57">
         <v>64.70002664089037</v>
       </c>
       <c r="E57">
-        <v>190.2321592215706</v>
+        <v>190.2321592215705</v>
       </c>
       <c r="F57">
         <v>27.110676433403</v>

--- a/Dados/PRODUTIVIDADE/table_PROD_TRIM_RS.xlsx
+++ b/Dados/PRODUTIVIDADE/table_PROD_TRIM_RS.xlsx
@@ -27561,25 +27561,25 @@
         <v>5.579155038397062</v>
       </c>
       <c r="D9">
-        <v>7.480615673841188</v>
+        <v>7.480615673841166</v>
       </c>
       <c r="E9">
         <v>6.813877184180154</v>
       </c>
       <c r="F9">
-        <v>0.4056911983870782</v>
+        <v>0.4056911983871191</v>
       </c>
       <c r="G9">
         <v>5.641090344201891</v>
       </c>
       <c r="H9">
-        <v>-0.04050097284610544</v>
+        <v>-0.04050097284613031</v>
       </c>
       <c r="I9">
         <v>5.139918156933014</v>
       </c>
       <c r="J9">
-        <v>3.664295484855633</v>
+        <v>3.664295484855651</v>
       </c>
       <c r="K9">
         <v>2.053226752511831</v>
@@ -27631,7 +27631,7 @@
         <v>5.107207205230286</v>
       </c>
       <c r="G10">
-        <v>6.717205861775713</v>
+        <v>6.71720586177574</v>
       </c>
       <c r="H10">
         <v>-0.5812917542175104</v>
@@ -27655,7 +27655,7 @@
         <v>-2.252075295562925</v>
       </c>
       <c r="O10">
-        <v>-0.1206092252127214</v>
+        <v>-0.1206092252127364</v>
       </c>
       <c r="P10">
         <v>5.868270124686999</v>
@@ -27664,10 +27664,10 @@
         <v>8.247862175902233</v>
       </c>
       <c r="R10">
-        <v>2.900785186115169</v>
+        <v>2.900785186115203</v>
       </c>
       <c r="S10">
-        <v>2.799666685937479</v>
+        <v>2.799666685937497</v>
       </c>
     </row>
     <row r="11">
@@ -27683,7 +27683,7 @@
         <v>28.28463126353658</v>
       </c>
       <c r="D11">
-        <v>2.648007406299392</v>
+        <v>2.648007406299372</v>
       </c>
       <c r="E11">
         <v>22.20705388227322</v>
@@ -27710,16 +27710,16 @@
         <v>6.340681357794264</v>
       </c>
       <c r="M11">
-        <v>-4.068002420951874</v>
+        <v>-4.068002420951832</v>
       </c>
       <c r="N11">
         <v>2.016925385214795</v>
       </c>
       <c r="O11">
-        <v>-0.7121955351673643</v>
+        <v>-0.7121955351673345</v>
       </c>
       <c r="P11">
-        <v>1.225518025900998</v>
+        <v>1.225518025901028</v>
       </c>
       <c r="Q11">
         <v>0.9173756770382873</v>
@@ -27728,7 +27728,7 @@
         <v>0.09971112554456942</v>
       </c>
       <c r="S11">
-        <v>-0.1492966507159569</v>
+        <v>-0.1492966507160091</v>
       </c>
     </row>
     <row r="12">
@@ -27741,34 +27741,34 @@
         <v>9.531686789744313</v>
       </c>
       <c r="C12">
-        <v>25.27064442715938</v>
+        <v>25.27064442715933</v>
       </c>
       <c r="D12">
         <v>-1.586963228080641</v>
       </c>
       <c r="E12">
-        <v>26.77685200971326</v>
+        <v>26.77685200971328</v>
       </c>
       <c r="F12">
         <v>2.050703167461934</v>
       </c>
       <c r="G12">
-        <v>0.5267046328180012</v>
+        <v>0.5267046328179891</v>
       </c>
       <c r="H12">
-        <v>0.8258894475904909</v>
+        <v>0.8258894475904535</v>
       </c>
       <c r="I12">
-        <v>11.11194316405574</v>
+        <v>11.1119431640557</v>
       </c>
       <c r="J12">
-        <v>-3.343155144880189</v>
+        <v>-3.343155144880206</v>
       </c>
       <c r="K12">
         <v>10.28654444148677</v>
       </c>
       <c r="L12">
-        <v>22.86431889509372</v>
+        <v>22.86431889509368</v>
       </c>
       <c r="M12">
         <v>-5.461257117346639</v>
@@ -27786,10 +27786,10 @@
         <v>0.1933112225220312</v>
       </c>
       <c r="R12">
-        <v>-1.322251989920461</v>
+        <v>-1.322251989920477</v>
       </c>
       <c r="S12">
-        <v>-1.607233293031634</v>
+        <v>-1.607233293031668</v>
       </c>
     </row>
     <row r="13">
@@ -27805,7 +27805,7 @@
         <v>19.82321213242447</v>
       </c>
       <c r="D13">
-        <v>-3.433020143316999</v>
+        <v>-3.43302014331698</v>
       </c>
       <c r="E13">
         <v>20.65972604497398</v>
@@ -27817,13 +27817,13 @@
         <v>-1.75132078664515</v>
       </c>
       <c r="H13">
-        <v>3.142494896324678</v>
+        <v>3.142494896324704</v>
       </c>
       <c r="I13">
         <v>8.137589751707253</v>
       </c>
       <c r="J13">
-        <v>-5.042818039382976</v>
+        <v>-5.042818039382993</v>
       </c>
       <c r="K13">
         <v>9.732796728712351</v>
@@ -27838,7 +27838,7 @@
         <v>2.665002463972055</v>
       </c>
       <c r="O13">
-        <v>-0.1012698837276898</v>
+        <v>-0.10126988372772</v>
       </c>
       <c r="P13">
         <v>0.5265296806198549</v>
@@ -27847,7 +27847,7 @@
         <v>-0.6672320698581001</v>
       </c>
       <c r="R13">
-        <v>-1.825107830530572</v>
+        <v>-1.825107830530588</v>
       </c>
       <c r="S13">
         <v>-2.146162445779148</v>
@@ -27863,7 +27863,7 @@
         <v>3.556311289603098</v>
       </c>
       <c r="C14">
-        <v>21.97455816828832</v>
+        <v>21.9745581682883</v>
       </c>
       <c r="D14">
         <v>-4.898465780841792</v>
@@ -27890,7 +27890,7 @@
         <v>1.39170912702208</v>
       </c>
       <c r="L14">
-        <v>20.53911735828523</v>
+        <v>20.5391173582852</v>
       </c>
       <c r="M14">
         <v>-6.266666240817553</v>
@@ -27899,7 +27899,7 @@
         <v>0.4166705646173953</v>
       </c>
       <c r="O14">
-        <v>-1.10058019631897</v>
+        <v>-1.100580196318955</v>
       </c>
       <c r="P14">
         <v>-1.11638080469877</v>
@@ -27908,10 +27908,10 @@
         <v>-2.250751356146834</v>
       </c>
       <c r="R14">
-        <v>-3.169374336508968</v>
+        <v>-3.169374336508984</v>
       </c>
       <c r="S14">
-        <v>-3.400219962252601</v>
+        <v>-3.400219962252652</v>
       </c>
     </row>
     <row r="15">
@@ -27927,7 +27927,7 @@
         <v>-6.959838425641335</v>
       </c>
       <c r="D15">
-        <v>-4.120512574107053</v>
+        <v>-4.120512574107034</v>
       </c>
       <c r="E15">
         <v>-8.32685217977787</v>
@@ -27954,10 +27954,10 @@
         <v>6.702270035154609</v>
       </c>
       <c r="M15">
-        <v>-3.96130624982297</v>
+        <v>-3.961306249822936</v>
       </c>
       <c r="N15">
-        <v>-1.343411957949131</v>
+        <v>-1.343411957949113</v>
       </c>
       <c r="O15">
         <v>-1.574822416320038</v>
@@ -27972,7 +27972,7 @@
         <v>-3.411124228632774</v>
       </c>
       <c r="S15">
-        <v>-3.566533467397621</v>
+        <v>-3.566533467397571</v>
       </c>
     </row>
     <row r="16">
@@ -27985,7 +27985,7 @@
         <v>10.88813820045842</v>
       </c>
       <c r="C16">
-        <v>-17.69395848740965</v>
+        <v>-17.69395848740963</v>
       </c>
       <c r="D16">
         <v>-5.611478996394957</v>
@@ -27997,13 +27997,13 @@
         <v>-2.694532936101357</v>
       </c>
       <c r="G16">
-        <v>-5.388884810088325</v>
+        <v>-5.388884810088301</v>
       </c>
       <c r="H16">
         <v>-4.414547830746681</v>
       </c>
       <c r="I16">
-        <v>-2.683080632577477</v>
+        <v>-2.683080632577511</v>
       </c>
       <c r="J16">
         <v>-13.48938719835177</v>
@@ -28030,10 +28030,10 @@
         <v>-2.809262810460161</v>
       </c>
       <c r="R16">
-        <v>-4.877499882058037</v>
+        <v>-4.87749988205802</v>
       </c>
       <c r="S16">
-        <v>-5.19271979515304</v>
+        <v>-5.192719795153007</v>
       </c>
     </row>
     <row r="17">
@@ -28082,7 +28082,7 @@
         <v>-2.573814660345377</v>
       </c>
       <c r="O17">
-        <v>-4.110431274079033</v>
+        <v>-4.110431274079004</v>
       </c>
       <c r="P17">
         <v>-3.296471974677899</v>
@@ -28091,7 +28091,7 @@
         <v>-4.44359163927859</v>
       </c>
       <c r="R17">
-        <v>-6.810186548289429</v>
+        <v>-6.810186548289413</v>
       </c>
       <c r="S17">
         <v>-7.235135180993852</v>
@@ -28107,7 +28107,7 @@
         <v>6.998419354982246</v>
       </c>
       <c r="C18">
-        <v>-25.64603970247646</v>
+        <v>-25.64603970247645</v>
       </c>
       <c r="D18">
         <v>-8.242009907697152</v>
@@ -28125,7 +28125,7 @@
         <v>-9.590021936858834</v>
       </c>
       <c r="I18">
-        <v>-12.98070178512799</v>
+        <v>-12.98070178512797</v>
       </c>
       <c r="J18">
         <v>-12.65173175964907</v>
@@ -28134,7 +28134,7 @@
         <v>-0.3179911161356538</v>
       </c>
       <c r="L18">
-        <v>7.315852961135187</v>
+        <v>7.315852961135211</v>
       </c>
       <c r="M18">
         <v>0.0287225306444804</v>
@@ -28143,19 +28143,19 @@
         <v>-1.531814920048603</v>
       </c>
       <c r="O18">
-        <v>-3.462466331347768</v>
+        <v>-3.462466331347737</v>
       </c>
       <c r="P18">
         <v>-3.344958284862541</v>
       </c>
       <c r="Q18">
-        <v>-4.638020661401433</v>
+        <v>-4.638020661401467</v>
       </c>
       <c r="R18">
-        <v>-6.439468285585389</v>
+        <v>-6.439468285585408</v>
       </c>
       <c r="S18">
-        <v>-6.915607977792772</v>
+        <v>-6.915607977792737</v>
       </c>
     </row>
     <row r="19">
@@ -28171,7 +28171,7 @@
         <v>-16.46439597303356</v>
       </c>
       <c r="D19">
-        <v>-8.15342343246626</v>
+        <v>-8.153423432466271</v>
       </c>
       <c r="E19">
         <v>-8.907626684273446</v>
@@ -28195,13 +28195,13 @@
         <v>-0.9674017995059074</v>
       </c>
       <c r="L19">
-        <v>17.97905078170907</v>
+        <v>17.97905078170909</v>
       </c>
       <c r="M19">
-        <v>0.5934574850539546</v>
+        <v>0.5934574850539187</v>
       </c>
       <c r="N19">
-        <v>-2.877847043025209</v>
+        <v>-2.877847043025227</v>
       </c>
       <c r="O19">
         <v>-2.421291498044443</v>
@@ -28229,7 +28229,7 @@
         <v>-1.011093337749203</v>
       </c>
       <c r="C20">
-        <v>-13.42933228488364</v>
+        <v>-13.42933228488362</v>
       </c>
       <c r="D20">
         <v>-5.605486921659102</v>
@@ -28241,13 +28241,13 @@
         <v>-9.441396332687287</v>
       </c>
       <c r="G20">
-        <v>-6.253963124723755</v>
+        <v>-6.253963124723778</v>
       </c>
       <c r="H20">
         <v>-4.850440958823544</v>
       </c>
       <c r="I20">
-        <v>-7.805519206792686</v>
+        <v>-7.805519206792677</v>
       </c>
       <c r="J20">
         <v>7.227638026611525</v>
@@ -28256,7 +28256,7 @@
         <v>-8.068332778656224</v>
       </c>
       <c r="L20">
-        <v>11.61377088965187</v>
+        <v>11.61377088965185</v>
       </c>
       <c r="M20">
         <v>0.4256774068238798</v>
@@ -28274,7 +28274,7 @@
         <v>-3.537685497039203</v>
       </c>
       <c r="R20">
-        <v>-4.012702437146075</v>
+        <v>-4.012702437146091</v>
       </c>
       <c r="S20">
         <v>-4.181269809024585</v>
@@ -28290,7 +28290,7 @@
         <v>-2.777960510522544</v>
       </c>
       <c r="C21">
-        <v>0.1428788372945786</v>
+        <v>0.1428788372946017</v>
       </c>
       <c r="D21">
         <v>-0.4044492264953712</v>
@@ -28305,7 +28305,7 @@
         <v>-2.363635658502645</v>
       </c>
       <c r="H21">
-        <v>-0.6570927133009623</v>
+        <v>-0.6570927133009357</v>
       </c>
       <c r="I21">
         <v>-2.474587107861761</v>
@@ -28329,7 +28329,7 @@
         <v>0.04597345216396228</v>
       </c>
       <c r="P21">
-        <v>-0.913839966933278</v>
+        <v>-0.9138399669332479</v>
       </c>
       <c r="Q21">
         <v>-1.313388196344187</v>
@@ -28338,7 +28338,7 @@
         <v>-1.122775588443872</v>
       </c>
       <c r="S21">
-        <v>-0.9657395786497275</v>
+        <v>-0.9657395786496896</v>
       </c>
     </row>
     <row r="22">
@@ -28360,7 +28360,7 @@
         <v>16.28141061270405</v>
       </c>
       <c r="F22">
-        <v>-7.579992549032236</v>
+        <v>-7.579992549032195</v>
       </c>
       <c r="G22">
         <v>0.2791820800871717</v>
@@ -28369,7 +28369,7 @@
         <v>0.5522609501210785</v>
       </c>
       <c r="I22">
-        <v>5.544782201053627</v>
+        <v>5.5447822010536</v>
       </c>
       <c r="J22">
         <v>16.41185650530121</v>
@@ -28381,22 +28381,22 @@
         <v>-5.901326265644291</v>
       </c>
       <c r="M22">
-        <v>-1.476858317791729</v>
+        <v>-1.476858317791753</v>
       </c>
       <c r="N22">
         <v>-0.885150536356729</v>
       </c>
       <c r="O22">
-        <v>0.2060677098903082</v>
+        <v>0.2060677098902765</v>
       </c>
       <c r="P22">
         <v>1.059693486916584</v>
       </c>
       <c r="Q22">
-        <v>1.218644171312721</v>
+        <v>1.218644171312756</v>
       </c>
       <c r="R22">
-        <v>-0.02700260307747224</v>
+        <v>-0.02700260307745457</v>
       </c>
       <c r="S22">
         <v>0.2373602850952193</v>
@@ -28415,7 +28415,7 @@
         <v>5.639908743549087</v>
       </c>
       <c r="D23">
-        <v>4.168493285317371</v>
+        <v>4.168493285317383</v>
       </c>
       <c r="E23">
         <v>6.654981089349048</v>
@@ -28433,13 +28433,13 @@
         <v>3.439126027670595</v>
       </c>
       <c r="J23">
-        <v>14.78957847725883</v>
+        <v>14.78957847725881</v>
       </c>
       <c r="K23">
         <v>-6.987082947061412</v>
       </c>
       <c r="L23">
-        <v>-17.97521331760915</v>
+        <v>-17.97521331760916</v>
       </c>
       <c r="M23">
         <v>-2.854783020873647</v>
@@ -28457,7 +28457,7 @@
         <v>2.189725707504138</v>
       </c>
       <c r="R23">
-        <v>0.5059600550758842</v>
+        <v>0.5059600550758664</v>
       </c>
       <c r="S23">
         <v>0.6749962538893168</v>
@@ -28473,13 +28473,13 @@
         <v>12.06080799058015</v>
       </c>
       <c r="C24">
-        <v>27.06392169985092</v>
+        <v>27.06392169985094</v>
       </c>
       <c r="D24">
         <v>4.447286488432891</v>
       </c>
       <c r="E24">
-        <v>-7.490547088611034</v>
+        <v>-7.490547088611019</v>
       </c>
       <c r="F24">
         <v>1.618105409606953</v>
@@ -28491,16 +28491,16 @@
         <v>2.701381757810038</v>
       </c>
       <c r="I24">
-        <v>1.16849858612291</v>
+        <v>1.168498586122935</v>
       </c>
       <c r="J24">
         <v>10.9388467268775</v>
       </c>
       <c r="K24">
-        <v>0.9576150762411662</v>
+        <v>0.9576150762411095</v>
       </c>
       <c r="L24">
-        <v>-20.38884852279677</v>
+        <v>-20.38884852279675</v>
       </c>
       <c r="M24">
         <v>-2.950270641951024</v>
@@ -28534,7 +28534,7 @@
         <v>14.27428419343944</v>
       </c>
       <c r="C25">
-        <v>11.14202771816517</v>
+        <v>11.14202771816514</v>
       </c>
       <c r="D25">
         <v>3.581371957031998</v>
@@ -28549,7 +28549,7 @@
         <v>3.801703966949666</v>
       </c>
       <c r="H25">
-        <v>4.527335587664894</v>
+        <v>4.527335587664866</v>
       </c>
       <c r="I25">
         <v>-3.080881081441516</v>
@@ -28558,22 +28558,22 @@
         <v>0.9618459103902975</v>
       </c>
       <c r="K25">
-        <v>9.384485269453114</v>
+        <v>9.384485269453156</v>
       </c>
       <c r="L25">
-        <v>-9.904272496464772</v>
+        <v>-9.904272496464793</v>
       </c>
       <c r="M25">
         <v>-2.150079370913727</v>
       </c>
       <c r="N25">
-        <v>0.9381726389041682</v>
+        <v>0.9381726389041295</v>
       </c>
       <c r="O25">
         <v>0.3678734707545768</v>
       </c>
       <c r="P25">
-        <v>2.703249143993363</v>
+        <v>2.703249143993331</v>
       </c>
       <c r="Q25">
         <v>3.223895118052527</v>
@@ -28582,7 +28582,7 @@
         <v>1.256231373216739</v>
       </c>
       <c r="S25">
-        <v>1.032818250858011</v>
+        <v>1.032818250857972</v>
       </c>
     </row>
     <row r="26">
@@ -28592,7 +28592,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>3.91419126612967</v>
+        <v>3.914191266129625</v>
       </c>
       <c r="C26">
         <v>-8.197089459784813</v>
@@ -28604,10 +28604,10 @@
         <v>-16.84628005552581</v>
       </c>
       <c r="F26">
-        <v>2.273941204013105</v>
+        <v>2.273941204013104</v>
       </c>
       <c r="G26">
-        <v>2.200753132754044</v>
+        <v>2.200753132754017</v>
       </c>
       <c r="H26">
         <v>6.635825182660313</v>
@@ -28625,7 +28625,7 @@
         <v>-8.031940805632713</v>
       </c>
       <c r="M26">
-        <v>0.3058446977093897</v>
+        <v>0.3058446977094139</v>
       </c>
       <c r="N26">
         <v>0.3369056085137011</v>
@@ -28640,10 +28640,10 @@
         <v>2.105930041472397</v>
       </c>
       <c r="R26">
-        <v>1.847695517176459</v>
+        <v>1.847695517176477</v>
       </c>
       <c r="S26">
-        <v>1.428397903471191</v>
+        <v>1.428397903471153</v>
       </c>
     </row>
     <row r="27">
@@ -28653,13 +28653,13 @@
         </is>
       </c>
       <c r="B27">
-        <v>-2.976019005308938</v>
+        <v>-2.976019005308952</v>
       </c>
       <c r="C27">
-        <v>-5.160751834804584</v>
+        <v>-5.160751834804617</v>
       </c>
       <c r="D27">
-        <v>-0.3575787781991607</v>
+        <v>-0.3575787781991393</v>
       </c>
       <c r="E27">
         <v>-16.24502760070524</v>
@@ -28668,7 +28668,7 @@
         <v>-2.838379046568128</v>
       </c>
       <c r="G27">
-        <v>-1.755761056294514</v>
+        <v>-1.755761056294488</v>
       </c>
       <c r="H27">
         <v>9.103982667875023</v>
@@ -28677,7 +28677,7 @@
         <v>-3.761146135157086</v>
       </c>
       <c r="J27">
-        <v>-2.533027083534665</v>
+        <v>-2.533027083534648</v>
       </c>
       <c r="K27">
         <v>13.78154949168186</v>
@@ -28698,10 +28698,10 @@
         <v>0.351765507069478</v>
       </c>
       <c r="Q27">
-        <v>0.9167444835337588</v>
+        <v>0.9167444835337759</v>
       </c>
       <c r="R27">
-        <v>1.846198413983245</v>
+        <v>1.846198413983263</v>
       </c>
       <c r="S27">
         <v>1.416533771553079</v>
@@ -28717,19 +28717,19 @@
         <v>-0.9436580388759375</v>
       </c>
       <c r="C28">
-        <v>-11.75131922094532</v>
+        <v>-11.75131922094533</v>
       </c>
       <c r="D28">
         <v>2.147558671036719</v>
       </c>
       <c r="E28">
-        <v>-5.415368308001959</v>
+        <v>-5.415368308001973</v>
       </c>
       <c r="F28">
         <v>-5.284027743140586</v>
       </c>
       <c r="G28">
-        <v>-0.2415965093201682</v>
+        <v>-0.2415965093201422</v>
       </c>
       <c r="H28">
         <v>8.846050130293914</v>
@@ -28741,10 +28741,10 @@
         <v>-5.456914521878937</v>
       </c>
       <c r="K28">
-        <v>16.72808187176472</v>
+        <v>16.72808187176479</v>
       </c>
       <c r="L28">
-        <v>16.05699958998594</v>
+        <v>16.05699958998597</v>
       </c>
       <c r="M28">
         <v>4.443612293255662</v>
@@ -28781,10 +28781,10 @@
         <v>10.41540946589188</v>
       </c>
       <c r="D29">
-        <v>3.766021949803755</v>
+        <v>3.766021949803776</v>
       </c>
       <c r="E29">
-        <v>2.997987681076951</v>
+        <v>2.997987681076967</v>
       </c>
       <c r="F29">
         <v>-8.095955612726335</v>
@@ -28802,16 +28802,16 @@
         <v>-10.68904705133618</v>
       </c>
       <c r="K29">
-        <v>19.04590524562659</v>
+        <v>19.04590524562654</v>
       </c>
       <c r="L29">
-        <v>7.108612648469226</v>
+        <v>7.108612648469252</v>
       </c>
       <c r="M29">
         <v>3.772124148534486</v>
       </c>
       <c r="N29">
-        <v>-1.683821530673351</v>
+        <v>-1.683821530673314</v>
       </c>
       <c r="O29">
         <v>3.488763809337213</v>
@@ -28836,7 +28836,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>-2.516462464997413</v>
+        <v>-2.516462464997415</v>
       </c>
       <c r="C30">
         <v>46.42609774404574</v>
@@ -28848,19 +28848,19 @@
         <v>7.975875367357751</v>
       </c>
       <c r="F30">
-        <v>-5.616463138477592</v>
+        <v>-5.616463138477633</v>
       </c>
       <c r="G30">
-        <v>2.764231602989535</v>
+        <v>2.764231602989561</v>
       </c>
       <c r="H30">
         <v>5.401514411277737</v>
       </c>
       <c r="I30">
-        <v>5.913638236287147</v>
+        <v>5.913638236287121</v>
       </c>
       <c r="J30">
-        <v>-15.56068933219696</v>
+        <v>-15.56068933219694</v>
       </c>
       <c r="K30">
         <v>14.22035601963283</v>
@@ -28887,7 +28887,7 @@
         <v>3.141222790596989</v>
       </c>
       <c r="S30">
-        <v>2.896637972852053</v>
+        <v>2.896637972852111</v>
       </c>
     </row>
     <row r="31">
@@ -28897,13 +28897,13 @@
         </is>
       </c>
       <c r="B31">
-        <v>2.660534354924291</v>
+        <v>2.660534354924306</v>
       </c>
       <c r="C31">
-        <v>49.28593035767681</v>
+        <v>49.28593035767689</v>
       </c>
       <c r="D31">
-        <v>9.279817836223723</v>
+        <v>9.279817836223701</v>
       </c>
       <c r="E31">
         <v>16.41492956942125</v>
@@ -28912,7 +28912,7 @@
         <v>-3.665266278366972</v>
       </c>
       <c r="G31">
-        <v>7.243830491174601</v>
+        <v>7.243830491174573</v>
       </c>
       <c r="H31">
         <v>3.040161956418557</v>
@@ -28936,13 +28936,13 @@
         <v>-4.312533831079418</v>
       </c>
       <c r="O31">
-        <v>-0.5120836407823666</v>
+        <v>-0.5120836407823972</v>
       </c>
       <c r="P31">
-        <v>2.817182058414621</v>
+        <v>2.81718205841465</v>
       </c>
       <c r="Q31">
-        <v>2.914523236209167</v>
+        <v>2.91452323620915</v>
       </c>
       <c r="R31">
         <v>2.981733364038777</v>
@@ -28964,7 +28964,7 @@
         <v>27.22843142683902</v>
       </c>
       <c r="D32">
-        <v>5.783950112380862</v>
+        <v>5.783950112380882</v>
       </c>
       <c r="E32">
         <v>16.69785618819273</v>
@@ -28973,7 +28973,7 @@
         <v>-0.4226035550114692</v>
       </c>
       <c r="G32">
-        <v>5.20954824043389</v>
+        <v>5.209548240433863</v>
       </c>
       <c r="H32">
         <v>-0.351883858465028</v>
@@ -28982,19 +28982,19 @@
         <v>-3.155968345264008</v>
       </c>
       <c r="J32">
-        <v>-17.72607535534273</v>
+        <v>-17.72607535534272</v>
       </c>
       <c r="K32">
         <v>10.8394727369829</v>
       </c>
       <c r="L32">
-        <v>3.196846499381362</v>
+        <v>3.196846499381317</v>
       </c>
       <c r="M32">
         <v>-4.052561988622696</v>
       </c>
       <c r="N32">
-        <v>-4.185620085791363</v>
+        <v>-4.185620085791383</v>
       </c>
       <c r="O32">
         <v>-2.500320589770932</v>
@@ -29009,7 +29009,7 @@
         <v>0.1983224677236551</v>
       </c>
       <c r="S32">
-        <v>0.01507905141971124</v>
+        <v>0.01507905141974818</v>
       </c>
     </row>
     <row r="33">
@@ -29019,16 +29019,16 @@
         </is>
       </c>
       <c r="B33">
-        <v>2.192027404518151</v>
+        <v>2.192027404518193</v>
       </c>
       <c r="C33">
         <v>-7.943058382779087</v>
       </c>
       <c r="D33">
-        <v>0.8373396733053985</v>
+        <v>0.8373396733053574</v>
       </c>
       <c r="E33">
-        <v>22.50737951725225</v>
+        <v>22.50737951725223</v>
       </c>
       <c r="F33">
         <v>0.9918760792399335</v>
@@ -29049,7 +29049,7 @@
         <v>9.720955050848687</v>
       </c>
       <c r="L33">
-        <v>7.632723500135615</v>
+        <v>7.632723500135591</v>
       </c>
       <c r="M33">
         <v>-3.748907512061253</v>
@@ -29070,7 +29070,7 @@
         <v>-1.909813743590625</v>
       </c>
       <c r="S33">
-        <v>-2.341287432187693</v>
+        <v>-2.341287432187656</v>
       </c>
     </row>
     <row r="34">
@@ -29080,7 +29080,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>3.387665110642109</v>
+        <v>3.387665110642154</v>
       </c>
       <c r="C34">
         <v>-23.41267676770779</v>
@@ -29101,22 +29101,22 @@
         <v>-2.755962964543293</v>
       </c>
       <c r="I34">
-        <v>-16.52489257245201</v>
+        <v>-16.52489257245199</v>
       </c>
       <c r="J34">
-        <v>-7.990110653110977</v>
+        <v>-7.990110653110997</v>
       </c>
       <c r="K34">
         <v>12.91703047722583</v>
       </c>
       <c r="L34">
-        <v>14.81675552260116</v>
+        <v>14.81675552260119</v>
       </c>
       <c r="M34">
         <v>-2.396830807422073</v>
       </c>
       <c r="N34">
-        <v>-5.255991794492305</v>
+        <v>-5.255991794492324</v>
       </c>
       <c r="O34">
         <v>-3.151491283903159</v>
@@ -29128,10 +29128,10 @@
         <v>-1.843564616052344</v>
       </c>
       <c r="R34">
-        <v>-2.676265913240722</v>
+        <v>-2.676265913240688</v>
       </c>
       <c r="S34">
-        <v>-3.272822667295317</v>
+        <v>-3.272822667295335</v>
       </c>
     </row>
     <row r="35">
@@ -29141,10 +29141,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-24.28850655537549</v>
+        <v>-24.28850655537546</v>
       </c>
       <c r="C35">
-        <v>-15.75501112798333</v>
+        <v>-15.75501112798335</v>
       </c>
       <c r="D35">
         <v>-7.661569217806958</v>
@@ -29177,13 +29177,13 @@
         <v>-3.547139171730603</v>
       </c>
       <c r="N35">
-        <v>-4.778865044154621</v>
+        <v>-4.778865044154641</v>
       </c>
       <c r="O35">
-        <v>-2.218615949721976</v>
+        <v>-2.218615949721946</v>
       </c>
       <c r="P35">
-        <v>-5.32212935921946</v>
+        <v>-5.322129359219486</v>
       </c>
       <c r="Q35">
         <v>-7.22407960816868</v>
@@ -29205,10 +29205,10 @@
         <v>-25.61909962182111</v>
       </c>
       <c r="C36">
-        <v>2.851309538925713</v>
+        <v>2.85130953892573</v>
       </c>
       <c r="D36">
-        <v>-5.056573421311862</v>
+        <v>-5.056573421311881</v>
       </c>
       <c r="E36">
         <v>24.00013270164992</v>
@@ -29223,22 +29223,22 @@
         <v>2.667763487341511</v>
       </c>
       <c r="I36">
-        <v>-13.44317858301982</v>
+        <v>-13.44317858301985</v>
       </c>
       <c r="J36">
-        <v>-0.5824043535528357</v>
+        <v>-0.582404353552847</v>
       </c>
       <c r="K36">
         <v>11.43136286313385</v>
       </c>
       <c r="L36">
-        <v>22.90595842222024</v>
+        <v>22.90595842222027</v>
       </c>
       <c r="M36">
-        <v>-2.405284637664173</v>
+        <v>-2.405284637664209</v>
       </c>
       <c r="N36">
-        <v>-3.332510677178664</v>
+        <v>-3.332510677178645</v>
       </c>
       <c r="O36">
         <v>0.587930837068227</v>
@@ -29253,7 +29253,7 @@
         <v>-0.8522091517933154</v>
       </c>
       <c r="S36">
-        <v>-2.086970825962895</v>
+        <v>-2.086970825962931</v>
       </c>
     </row>
     <row r="37">
@@ -29263,13 +29263,13 @@
         </is>
       </c>
       <c r="B37">
-        <v>-31.8301219584438</v>
+        <v>-31.83012195844383</v>
       </c>
       <c r="C37">
-        <v>47.25717733317327</v>
+        <v>47.25717733317329</v>
       </c>
       <c r="D37">
-        <v>4.056817405082012</v>
+        <v>4.056817405082033</v>
       </c>
       <c r="E37">
         <v>1.899186775192946</v>
@@ -29293,13 +29293,13 @@
         <v>-9.605579959751317</v>
       </c>
       <c r="L37">
-        <v>43.2794939452731</v>
+        <v>43.27949394527311</v>
       </c>
       <c r="M37">
         <v>-0.2168559977723349</v>
       </c>
       <c r="N37">
-        <v>-2.537130124404639</v>
+        <v>-2.53713012440466</v>
       </c>
       <c r="O37">
         <v>3.034395231696828</v>
@@ -29311,10 +29311,10 @@
         <v>-2.363628696067953</v>
       </c>
       <c r="R37">
-        <v>3.494030845907109</v>
+        <v>3.494030845907143</v>
       </c>
       <c r="S37">
-        <v>2.90050124408166</v>
+        <v>2.900501244081621</v>
       </c>
     </row>
     <row r="38">
@@ -29354,13 +29354,13 @@
         <v>-28.06321115658877</v>
       </c>
       <c r="L38">
-        <v>45.69659263696378</v>
+        <v>45.69659263696375</v>
       </c>
       <c r="M38">
         <v>0.7184386191705671</v>
       </c>
       <c r="N38">
-        <v>0.6622229977464713</v>
+        <v>0.6622229977464922</v>
       </c>
       <c r="O38">
         <v>4.354633452865883</v>
@@ -29372,7 +29372,7 @@
         <v>1.106708142065965</v>
       </c>
       <c r="R38">
-        <v>6.736064818670852</v>
+        <v>6.736064818670814</v>
       </c>
       <c r="S38">
         <v>6.929693112591315</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>27.54321807288549</v>
+        <v>27.54321807288545</v>
       </c>
       <c r="C39">
         <v>14.60554887999615</v>
@@ -29421,19 +29421,19 @@
         <v>8.315663978958565</v>
       </c>
       <c r="N39">
-        <v>2.926630867918549</v>
+        <v>2.926630867918571</v>
       </c>
       <c r="O39">
-        <v>5.696981342647264</v>
+        <v>5.696981342647248</v>
       </c>
       <c r="P39">
-        <v>12.2942369320536</v>
+        <v>12.29423693205358</v>
       </c>
       <c r="Q39">
-        <v>13.47448825271981</v>
+        <v>13.47448825271983</v>
       </c>
       <c r="R39">
-        <v>11.24126890834369</v>
+        <v>11.24126890834367</v>
       </c>
       <c r="S39">
         <v>13.24005274860325</v>
@@ -29449,7 +29449,7 @@
         <v>28.23910430029164</v>
       </c>
       <c r="C40">
-        <v>-6.254979924095593</v>
+        <v>-6.254979924095609</v>
       </c>
       <c r="D40">
         <v>20.1432236809034</v>
@@ -29467,7 +29467,7 @@
         <v>-0.7388211816217685</v>
       </c>
       <c r="I40">
-        <v>15.47892610148327</v>
+        <v>15.47892610148332</v>
       </c>
       <c r="J40">
         <v>-0.5872261682502629</v>
@@ -29476,10 +29476,10 @@
         <v>-41.9110895699262</v>
       </c>
       <c r="L40">
-        <v>25.98594653843745</v>
+        <v>25.98594653843742</v>
       </c>
       <c r="M40">
-        <v>8.232612894259233</v>
+        <v>8.232612894259274</v>
       </c>
       <c r="N40">
         <v>1.104685015357698</v>
@@ -29537,25 +29537,25 @@
         <v>-30.19633850349371</v>
       </c>
       <c r="L41">
-        <v>-4.802174185630348</v>
+        <v>-4.802174185630334</v>
       </c>
       <c r="M41">
         <v>5.337945076401447</v>
       </c>
       <c r="N41">
-        <v>0.5728308097907699</v>
+        <v>0.572830809790791</v>
       </c>
       <c r="O41">
-        <v>0.4944280905162245</v>
+        <v>0.4944280905162093</v>
       </c>
       <c r="P41">
-        <v>5.501236855349706</v>
+        <v>5.501236855349676</v>
       </c>
       <c r="Q41">
         <v>7.79501942757812</v>
       </c>
       <c r="R41">
-        <v>3.080480485825946</v>
+        <v>3.080480485825912</v>
       </c>
       <c r="S41">
         <v>5.183746576241836</v>
@@ -29568,7 +29568,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>22.1337033126641</v>
+        <v>22.13370331266408</v>
       </c>
       <c r="C42">
         <v>-33.38067014156794</v>
@@ -29604,10 +29604,10 @@
         <v>5.086368605756147</v>
       </c>
       <c r="N42">
-        <v>-0.8470794827063616</v>
+        <v>-0.8470794827063408</v>
       </c>
       <c r="O42">
-        <v>-0.9132563684551963</v>
+        <v>-0.9132563684552265</v>
       </c>
       <c r="P42">
         <v>0.4982228142017909</v>
@@ -29650,7 +29650,7 @@
         <v>-2.853652398724674</v>
       </c>
       <c r="I43">
-        <v>-0.8041882615615377</v>
+        <v>-0.8041882615615639</v>
       </c>
       <c r="J43">
         <v>15.07995129392086</v>
@@ -29668,16 +29668,16 @@
         <v>-1.801153416872759</v>
       </c>
       <c r="O43">
-        <v>-2.913617118202916</v>
+        <v>-2.913617118202871</v>
       </c>
       <c r="P43">
-        <v>-9.517324569568784</v>
+        <v>-9.517324569568773</v>
       </c>
       <c r="Q43">
-        <v>-9.892959440862503</v>
+        <v>-9.892959440862517</v>
       </c>
       <c r="R43">
-        <v>-4.444223838850652</v>
+        <v>-4.444223838850653</v>
       </c>
       <c r="S43">
         <v>-4.008925664130319</v>
@@ -29693,7 +29693,7 @@
         <v>-39.08707009627206</v>
       </c>
       <c r="C44">
-        <v>-4.996989542157</v>
+        <v>-4.996989542156983</v>
       </c>
       <c r="D44">
         <v>-12.99237616618986</v>
@@ -29702,7 +29702,7 @@
         <v>19.17825528880849</v>
       </c>
       <c r="F44">
-        <v>-4.738355784315382</v>
+        <v>-4.738355784315421</v>
       </c>
       <c r="G44">
         <v>-9.794159925538249</v>
@@ -29714,13 +29714,13 @@
         <v>-2.555553995879511</v>
       </c>
       <c r="J44">
-        <v>16.32279448439473</v>
+        <v>16.32279448439471</v>
       </c>
       <c r="K44">
         <v>13.60606337289016</v>
       </c>
       <c r="L44">
-        <v>-47.60429151232985</v>
+        <v>-47.60429151232984</v>
       </c>
       <c r="M44">
         <v>-1.104462465788272</v>
@@ -29766,7 +29766,7 @@
         <v>-3.932514773418756</v>
       </c>
       <c r="G45">
-        <v>-10.14179543906422</v>
+        <v>-10.1417954390642</v>
       </c>
       <c r="H45">
         <v>1.662149061634382</v>
@@ -29784,22 +29784,22 @@
         <v>-44.69794780212701</v>
       </c>
       <c r="M45">
-        <v>0.8775093981673275</v>
+        <v>0.8775093981672927</v>
       </c>
       <c r="N45">
         <v>0.7456306719460856</v>
       </c>
       <c r="O45">
-        <v>-1.784253642514346</v>
+        <v>-1.784253642514316</v>
       </c>
       <c r="P45">
-        <v>-9.116263584594011</v>
+        <v>-9.116263584593986</v>
       </c>
       <c r="Q45">
-        <v>-9.808739148767117</v>
+        <v>-9.808739148767101</v>
       </c>
       <c r="R45">
-        <v>-4.119967581200084</v>
+        <v>-4.119967581200117</v>
       </c>
       <c r="S45">
         <v>-4.040909916918427</v>
@@ -29812,16 +29812,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>-32.79702495854226</v>
+        <v>-32.79702495854222</v>
       </c>
       <c r="C46">
         <v>35.95962117893655</v>
       </c>
       <c r="D46">
-        <v>-16.38662000072259</v>
+        <v>-16.38662000072258</v>
       </c>
       <c r="E46">
-        <v>31.5551225120221</v>
+        <v>31.555122512022</v>
       </c>
       <c r="F46">
         <v>-3.149803323734631</v>
@@ -29836,13 +29836,13 @@
         <v>-6.783456499382192</v>
       </c>
       <c r="J46">
-        <v>0.5203186936150829</v>
+        <v>0.5203186936151042</v>
       </c>
       <c r="K46">
         <v>-0.4154891942341013</v>
       </c>
       <c r="L46">
-        <v>-27.9434555971778</v>
+        <v>-27.94345559717778</v>
       </c>
       <c r="M46">
         <v>0.3196692977043216</v>
@@ -29851,7 +29851,7 @@
         <v>1.605464394918505</v>
       </c>
       <c r="O46">
-        <v>-0.7952181924831747</v>
+        <v>-0.7952181924831445</v>
       </c>
       <c r="P46">
         <v>-7.250982803180465</v>
@@ -29863,7 +29863,7 @@
         <v>-4.142737829079358</v>
       </c>
       <c r="S46">
-        <v>-4.121290636856275</v>
+        <v>-4.12129063685624</v>
       </c>
     </row>
     <row r="47">
@@ -29894,7 +29894,7 @@
         <v>3.278009812859982</v>
       </c>
       <c r="I47">
-        <v>2.268406462074267</v>
+        <v>2.268406462074295</v>
       </c>
       <c r="J47">
         <v>-7.184890695269548</v>
@@ -29912,7 +29912,7 @@
         <v>2.967554337107828</v>
       </c>
       <c r="O47">
-        <v>0.4861566379750252</v>
+        <v>0.4861566379749943</v>
       </c>
       <c r="P47">
         <v>-1.128100470101287</v>
@@ -29921,7 +29921,7 @@
         <v>-0.8904889686468362</v>
       </c>
       <c r="R47">
-        <v>-4.082782509866134</v>
+        <v>-4.082782509866119</v>
       </c>
       <c r="S47">
         <v>-4.160258990645108</v>
@@ -29937,7 +29937,7 @@
         <v>28.77727286513237</v>
       </c>
       <c r="C48">
-        <v>13.33991175461196</v>
+        <v>13.3399117546119</v>
       </c>
       <c r="D48">
         <v>-12.61305170954677</v>
@@ -29946,7 +29946,7 @@
         <v>11.04522555697126</v>
       </c>
       <c r="F48">
-        <v>-9.022883908058763</v>
+        <v>-9.022883908058725</v>
       </c>
       <c r="G48">
         <v>-11.06696716853014</v>
@@ -29958,7 +29958,7 @@
         <v>4.790190094974611</v>
       </c>
       <c r="J48">
-        <v>-12.11621616850793</v>
+        <v>-12.1162161685079</v>
       </c>
       <c r="K48">
         <v>-7.410046034631238</v>
@@ -29973,10 +29973,10 @@
         <v>2.669775007766403</v>
       </c>
       <c r="O48">
-        <v>1.109673808866593</v>
+        <v>1.109673808866562</v>
       </c>
       <c r="P48">
-        <v>0.2701550771917008</v>
+        <v>0.2701550771916856</v>
       </c>
       <c r="Q48">
         <v>0.07695189324018117</v>
@@ -30010,7 +30010,7 @@
         <v>-9.087996207474148</v>
       </c>
       <c r="G49">
-        <v>-8.202366525934275</v>
+        <v>-8.202366525934298</v>
       </c>
       <c r="H49">
         <v>4.388606680874128</v>
@@ -30028,10 +30028,10 @@
         <v>15.62568285562606</v>
       </c>
       <c r="M49">
-        <v>-0.7313068709483674</v>
+        <v>-0.7313068709483332</v>
       </c>
       <c r="N49">
-        <v>3.351312917305477</v>
+        <v>3.351312917305498</v>
       </c>
       <c r="O49">
         <v>1.499439237175889</v>
@@ -30040,10 +30040,10 @@
         <v>1.161842283291769</v>
       </c>
       <c r="Q49">
-        <v>0.6553575735625818</v>
+        <v>0.6553575735625465</v>
       </c>
       <c r="R49">
-        <v>-2.253615955522547</v>
+        <v>-2.253615955522514</v>
       </c>
       <c r="S49">
         <v>-2.58986003202813</v>
@@ -30056,22 +30056,22 @@
         </is>
       </c>
       <c r="B50">
-        <v>41.64198639444642</v>
+        <v>41.64198639444636</v>
       </c>
       <c r="C50">
-        <v>-9.092115248570499</v>
+        <v>-9.092115248570467</v>
       </c>
       <c r="D50">
-        <v>-2.830693881726011</v>
+        <v>-2.83069388172601</v>
       </c>
       <c r="E50">
-        <v>15.15038513346907</v>
+        <v>15.15038513346916</v>
       </c>
       <c r="F50">
         <v>-7.568487691605585</v>
       </c>
       <c r="G50">
-        <v>-2.984505600236339</v>
+        <v>-2.984505600236365</v>
       </c>
       <c r="H50">
         <v>1.809575683889947</v>
@@ -30080,19 +30080,19 @@
         <v>6.998299116785762</v>
       </c>
       <c r="J50">
-        <v>-5.752178057540176</v>
+        <v>-5.752178057540197</v>
       </c>
       <c r="K50">
         <v>-2.826517786527582</v>
       </c>
       <c r="L50">
-        <v>3.02603037137298</v>
+        <v>3.026030371372979</v>
       </c>
       <c r="M50">
         <v>-0.3522186146996085</v>
       </c>
       <c r="N50">
-        <v>2.359989693413708</v>
+        <v>2.359989693413687</v>
       </c>
       <c r="O50">
         <v>0.8325811425615507</v>
@@ -30104,10 +30104,10 @@
         <v>3.567928683495792</v>
       </c>
       <c r="R50">
-        <v>-0.6501527698652828</v>
+        <v>-0.6501527698653339</v>
       </c>
       <c r="S50">
-        <v>-0.9606905860508097</v>
+        <v>-0.960690586050846</v>
       </c>
     </row>
     <row r="51">
@@ -30123,7 +30123,7 @@
         <v>-9.637237638949497</v>
       </c>
       <c r="D51">
-        <v>-1.463212210090213</v>
+        <v>-1.463212210090235</v>
       </c>
       <c r="E51">
         <v>22.78424903144489</v>
@@ -30141,13 +30141,13 @@
         <v>-0.3065369563819829</v>
       </c>
       <c r="J51">
-        <v>1.967351355990913</v>
+        <v>1.967351355990935</v>
       </c>
       <c r="K51">
         <v>7.278734975633354</v>
       </c>
       <c r="L51">
-        <v>-6.410511052172727</v>
+        <v>-6.410511052172701</v>
       </c>
       <c r="M51">
         <v>-0.0140321101346271</v>
@@ -30156,13 +30156,13 @@
         <v>-0.04820038597932786</v>
       </c>
       <c r="O51">
-        <v>0.3343152499276419</v>
+        <v>0.3343152499276114</v>
       </c>
       <c r="P51">
-        <v>3.151762847443124</v>
+        <v>3.151762847443109</v>
       </c>
       <c r="Q51">
-        <v>4.438342848875835</v>
+        <v>4.43834284887587</v>
       </c>
       <c r="R51">
         <v>0.5069811675622428</v>
@@ -30181,7 +30181,7 @@
         <v>37.83293372791745</v>
       </c>
       <c r="C52">
-        <v>15.04746399365953</v>
+        <v>15.04746399365956</v>
       </c>
       <c r="D52">
         <v>-1.931512134500795</v>
@@ -30193,16 +30193,16 @@
         <v>1.370969136234461</v>
       </c>
       <c r="G52">
-        <v>0.862064728664458</v>
+        <v>0.8620647286644446</v>
       </c>
       <c r="H52">
-        <v>0.01163670515763778</v>
+        <v>0.01163670515760386</v>
       </c>
       <c r="I52">
         <v>-5.402161538340723</v>
       </c>
       <c r="J52">
-        <v>7.046366576726976</v>
+        <v>7.046366576726965</v>
       </c>
       <c r="K52">
         <v>12.61621017155069</v>
@@ -30211,25 +30211,25 @@
         <v>-9.980392062584899</v>
       </c>
       <c r="M52">
-        <v>2.093558438515651</v>
+        <v>2.093558438515686</v>
       </c>
       <c r="N52">
         <v>-2.658941446362987</v>
       </c>
       <c r="O52">
-        <v>-0.2799081618693519</v>
+        <v>-0.2799081618693215</v>
       </c>
       <c r="P52">
-        <v>3.130518680837337</v>
+        <v>3.130518680837352</v>
       </c>
       <c r="Q52">
-        <v>4.622134405595883</v>
+        <v>4.622134405595848</v>
       </c>
       <c r="R52">
-        <v>0.5737979907837421</v>
+        <v>0.5737979907837593</v>
       </c>
       <c r="S52">
-        <v>0.2375132368461635</v>
+        <v>0.2375132368461265</v>
       </c>
     </row>
     <row r="53">
@@ -30239,7 +30239,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>46.58821007422159</v>
+        <v>46.58821007422154</v>
       </c>
       <c r="C53">
         <v>26.34636334453065</v>
@@ -30260,7 +30260,7 @@
         <v>0.08720220506846253</v>
       </c>
       <c r="I53">
-        <v>-7.947110320270704</v>
+        <v>-7.947110320270742</v>
       </c>
       <c r="J53">
         <v>3.743539456881226</v>
@@ -30275,16 +30275,16 @@
         <v>3.116959617034</v>
       </c>
       <c r="N53">
-        <v>-3.079633239840859</v>
+        <v>-3.079633239840878</v>
       </c>
       <c r="O53">
-        <v>-0.2167236897547263</v>
+        <v>-0.2167236897547111</v>
       </c>
       <c r="P53">
         <v>3.758926511781641</v>
       </c>
       <c r="Q53">
-        <v>5.38404389776235</v>
+        <v>5.384043897762368</v>
       </c>
       <c r="R53">
         <v>0.6010373223717553</v>
@@ -30303,10 +30303,10 @@
         <v>31.77127865317716</v>
       </c>
       <c r="C54">
-        <v>46.6069867174043</v>
+        <v>46.60698671740424</v>
       </c>
       <c r="D54">
-        <v>-3.778174396782804</v>
+        <v>-3.778174396782826</v>
       </c>
       <c r="E54">
         <v>3.25321125018902</v>
@@ -30315,10 +30315,10 @@
         <v>7.764659302612118</v>
       </c>
       <c r="G54">
-        <v>-0.9545776539840822</v>
+        <v>-0.9545776539840559</v>
       </c>
       <c r="H54">
-        <v>1.475816730499172</v>
+        <v>1.475816730499149</v>
       </c>
       <c r="I54">
         <v>-11.73775780487665</v>
@@ -30327,10 +30327,10 @@
         <v>8.956739497015565</v>
       </c>
       <c r="K54">
-        <v>17.07635835632189</v>
+        <v>17.07635835632196</v>
       </c>
       <c r="L54">
-        <v>-4.130633477158352</v>
+        <v>-4.130633477158377</v>
       </c>
       <c r="M54">
         <v>2.902075409916364</v>
@@ -30348,7 +30348,7 @@
         <v>3.772555122008582</v>
       </c>
       <c r="R54">
-        <v>0.2536340498798303</v>
+        <v>0.2536340498798819</v>
       </c>
       <c r="S54">
         <v>-0.1919040996529383</v>
@@ -30364,13 +30364,13 @@
         <v>-1.703439443579288</v>
       </c>
       <c r="C55">
-        <v>59.99203529260644</v>
+        <v>59.99203529260647</v>
       </c>
       <c r="D55">
-        <v>-1.041302167719581</v>
+        <v>-1.041302167719559</v>
       </c>
       <c r="E55">
-        <v>-1.06559387205066</v>
+        <v>-1.065593872050597</v>
       </c>
       <c r="F55">
         <v>7.485637707289343</v>
@@ -30379,19 +30379,19 @@
         <v>0.3298598898587922</v>
       </c>
       <c r="H55">
-        <v>1.498819209299502</v>
+        <v>1.498819209299547</v>
       </c>
       <c r="I55">
-        <v>-8.918551416510402</v>
+        <v>-8.918551416510363</v>
       </c>
       <c r="J55">
-        <v>6.789177261886454</v>
+        <v>6.789177261886431</v>
       </c>
       <c r="K55">
         <v>2.165089801586305</v>
       </c>
       <c r="L55">
-        <v>5.795782719744439</v>
+        <v>5.795782719744409</v>
       </c>
       <c r="M55">
         <v>2.164979947761835</v>
@@ -30400,13 +30400,13 @@
         <v>-5.328836744770375</v>
       </c>
       <c r="O55">
-        <v>-0.5954354607857995</v>
+        <v>-0.5954354607857539</v>
       </c>
       <c r="P55">
-        <v>-0.4125857621995651</v>
+        <v>-0.4125857621995505</v>
       </c>
       <c r="Q55">
-        <v>0.0001814391927202355</v>
+        <v>0.0001814391926868295</v>
       </c>
       <c r="R55">
         <v>0.4331413673385487</v>
@@ -30422,13 +30422,13 @@
         </is>
       </c>
       <c r="B56">
-        <v>-3.928605193790596</v>
+        <v>-3.928605193790568</v>
       </c>
       <c r="C56">
         <v>48.279270422538</v>
       </c>
       <c r="D56">
-        <v>0.3551901573482854</v>
+        <v>0.355190157348297</v>
       </c>
       <c r="E56">
         <v>1.023011745298999</v>
@@ -30437,10 +30437,10 @@
         <v>7.511174917408169</v>
       </c>
       <c r="G56">
-        <v>1.65780953025026</v>
+        <v>1.657809530250273</v>
       </c>
       <c r="H56">
-        <v>2.74213399557368</v>
+        <v>2.74213399557376</v>
       </c>
       <c r="I56">
         <v>-8.77824854929303</v>
@@ -30455,7 +30455,7 @@
         <v>12.88097459097703</v>
       </c>
       <c r="M56">
-        <v>1.128440354707265</v>
+        <v>1.128440354707231</v>
       </c>
       <c r="N56">
         <v>-3.541199408382536</v>
@@ -30467,13 +30467,13 @@
         <v>-0.2692538432909591</v>
       </c>
       <c r="Q56">
-        <v>-0.1140707166296621</v>
+        <v>-0.1140707166296289</v>
       </c>
       <c r="R56">
-        <v>0.6202254363989156</v>
+        <v>0.6202254363988984</v>
       </c>
       <c r="S56">
-        <v>0.7621154969849456</v>
+        <v>0.7621154969849828</v>
       </c>
     </row>
     <row r="57">
@@ -30483,7 +30483,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>-4.200601845096995</v>
+        <v>-4.200601845096969</v>
       </c>
       <c r="C57">
         <v>75.44417505826056</v>
@@ -30504,7 +30504,7 @@
         <v>0.9298962089861935</v>
       </c>
       <c r="I57">
-        <v>-4.908445354939149</v>
+        <v>-4.90844535493911</v>
       </c>
       <c r="J57">
         <v>5.579943673948613</v>
@@ -30522,7 +30522,7 @@
         <v>-4.204191823993397</v>
       </c>
       <c r="O57">
-        <v>-0.5857932822294378</v>
+        <v>-0.5857932822294681</v>
       </c>
       <c r="P57">
         <v>-0.01019091096193629</v>
@@ -30534,7 +30534,7 @@
         <v>0.9516883380306264</v>
       </c>
       <c r="S57">
-        <v>1.21218713162744</v>
+        <v>1.212187131627477</v>
       </c>
     </row>
     <row r="58">
@@ -30707,16 +30707,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>63.0370613012719</v>
+        <v>63.03706130127185</v>
       </c>
       <c r="C9">
         <v>3.076729180067361</v>
       </c>
       <c r="D9">
-        <v>7.34753410815539</v>
+        <v>7.347534108155351</v>
       </c>
       <c r="E9">
-        <v>8.020144944203052</v>
+        <v>8.020144944203066</v>
       </c>
       <c r="F9">
         <v>0.9107958112520573</v>
@@ -30728,7 +30728,7 @@
         <v>0.3533274450670978</v>
       </c>
       <c r="I9">
-        <v>4.444479975507732</v>
+        <v>4.444479975507769</v>
       </c>
       <c r="J9">
         <v>2.804770250175989</v>
@@ -30749,16 +30749,16 @@
         <v>-0.07021682267661804</v>
       </c>
       <c r="P9">
-        <v>5.961480095192788</v>
+        <v>5.961480095192803</v>
       </c>
       <c r="Q9">
         <v>9.032215084700374</v>
       </c>
       <c r="R9">
-        <v>3.268594070217422</v>
+        <v>3.268594070217407</v>
       </c>
       <c r="S9">
-        <v>3.273319455818149</v>
+        <v>3.273319455818114</v>
       </c>
     </row>
     <row r="10">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>52.2804966043221</v>
+        <v>52.28049660432215</v>
       </c>
       <c r="C10">
         <v>5.45607050454909</v>
@@ -30795,10 +30795,10 @@
         <v>1.345456829724072</v>
       </c>
       <c r="K10">
-        <v>5.714253092502273</v>
+        <v>5.71425309250233</v>
       </c>
       <c r="L10">
-        <v>-12.27070262661996</v>
+        <v>-12.27070262661997</v>
       </c>
       <c r="M10">
         <v>-1.758090682160077</v>
@@ -30816,7 +30816,7 @@
         <v>7.11771160262009</v>
       </c>
       <c r="R10">
-        <v>1.862861369026172</v>
+        <v>1.86286136902614</v>
       </c>
       <c r="S10">
         <v>1.776547209044814</v>
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>4.721310090537288</v>
+        <v>4.721310090537268</v>
       </c>
       <c r="C11">
         <v>33.82749360036004</v>
@@ -30847,22 +30847,22 @@
         <v>2.944457736513957</v>
       </c>
       <c r="H11">
-        <v>-1.186911714751985</v>
+        <v>-1.18691171475202</v>
       </c>
       <c r="I11">
         <v>9.642281151223839</v>
       </c>
       <c r="J11">
-        <v>-0.5158351155202441</v>
+        <v>-0.5158351155202612</v>
       </c>
       <c r="K11">
         <v>9.634722237304409</v>
       </c>
       <c r="L11">
-        <v>3.596273312118471</v>
+        <v>3.596273312118458</v>
       </c>
       <c r="M11">
-        <v>-5.012467473727689</v>
+        <v>-5.01246747372767</v>
       </c>
       <c r="N11">
         <v>1.256092107001363</v>
@@ -30871,16 +30871,16 @@
         <v>-1.468529237305785</v>
       </c>
       <c r="P11">
-        <v>0.6120179255466079</v>
+        <v>0.6120179255466358</v>
       </c>
       <c r="Q11">
-        <v>0.3422374163040992</v>
+        <v>0.3422374163040677</v>
       </c>
       <c r="R11">
         <v>-0.4901244599846117</v>
       </c>
       <c r="S11">
-        <v>-0.7302626066244328</v>
+        <v>-0.7302626066244823</v>
       </c>
     </row>
     <row r="12">
@@ -30890,10 +30890,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>9.225746388241074</v>
+        <v>9.225746388241076</v>
       </c>
       <c r="C12">
-        <v>31.6277552893691</v>
+        <v>31.62775528936905</v>
       </c>
       <c r="D12">
         <v>-1.388336028103323</v>
@@ -30908,13 +30908,13 @@
         <v>0.2252589499369847</v>
       </c>
       <c r="H12">
-        <v>0.1615860215412023</v>
+        <v>0.1615860215412022</v>
       </c>
       <c r="I12">
-        <v>11.03417300608307</v>
+        <v>11.03417300608303</v>
       </c>
       <c r="J12">
-        <v>-5.331381922948622</v>
+        <v>-5.331381922948607</v>
       </c>
       <c r="K12">
         <v>9.366952896723779</v>
@@ -30929,7 +30929,7 @@
         <v>3.145770074901141</v>
       </c>
       <c r="O12">
-        <v>-1.055396824734295</v>
+        <v>-1.055396824734323</v>
       </c>
       <c r="P12">
         <v>0.6162191311961338</v>
@@ -30951,13 +30951,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>6.422375357728767</v>
+        <v>6.422375357728805</v>
       </c>
       <c r="C13">
         <v>28.88535194634531</v>
       </c>
       <c r="D13">
-        <v>-2.724574038796602</v>
+        <v>-2.724574038796584</v>
       </c>
       <c r="E13">
         <v>19.43126501636291</v>
@@ -30972,7 +30972,7 @@
         <v>2.956375991757636</v>
       </c>
       <c r="I13">
-        <v>9.174635389255901</v>
+        <v>9.174635389255863</v>
       </c>
       <c r="J13">
         <v>-5.844197512729614</v>
@@ -30981,25 +30981,25 @@
         <v>8.362122587217408</v>
       </c>
       <c r="L13">
-        <v>19.05216258974761</v>
+        <v>19.05216258974759</v>
       </c>
       <c r="M13">
         <v>-5.612852303182025</v>
       </c>
       <c r="N13">
-        <v>3.554598234194438</v>
+        <v>3.55459823419442</v>
       </c>
       <c r="O13">
-        <v>-0.1786943533715752</v>
+        <v>-0.1786943533715896</v>
       </c>
       <c r="P13">
-        <v>0.5745031183055341</v>
+        <v>0.5745031183055063</v>
       </c>
       <c r="Q13">
         <v>-0.6729324200447302</v>
       </c>
       <c r="R13">
-        <v>-1.841316048086911</v>
+        <v>-1.841316048086896</v>
       </c>
       <c r="S13">
         <v>-2.142577139799252</v>
@@ -31012,13 +31012,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>4.783710413007202</v>
+        <v>4.783710413007166</v>
       </c>
       <c r="C14">
         <v>21.62276920751207</v>
       </c>
       <c r="D14">
-        <v>-4.310599332868968</v>
+        <v>-4.310599332868949</v>
       </c>
       <c r="E14">
         <v>7.382160660647037</v>
@@ -31042,19 +31042,19 @@
         <v>1.52675844454081</v>
       </c>
       <c r="L14">
-        <v>17.65787655084113</v>
+        <v>17.65787655084115</v>
       </c>
       <c r="M14">
-        <v>-5.865563162308022</v>
+        <v>-5.865563162308055</v>
       </c>
       <c r="N14">
-        <v>1.840267372890433</v>
+        <v>1.840267372890451</v>
       </c>
       <c r="O14">
         <v>-0.8471491702840939</v>
       </c>
       <c r="P14">
-        <v>-0.7293893274209162</v>
+        <v>-0.7293893274209023</v>
       </c>
       <c r="Q14">
         <v>-1.949048069618092</v>
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>14.74056739284623</v>
+        <v>14.74056739284621</v>
       </c>
       <c r="C15">
         <v>-12.84059865204704</v>
@@ -31094,16 +31094,16 @@
         <v>0.2563628072688924</v>
       </c>
       <c r="I15">
-        <v>1.038458837743317</v>
+        <v>1.038458837743274</v>
       </c>
       <c r="J15">
-        <v>-11.45283415208803</v>
+        <v>-11.45283415208801</v>
       </c>
       <c r="K15">
         <v>-4.115819878034567</v>
       </c>
       <c r="L15">
-        <v>3.826052239936775</v>
+        <v>3.826052239936763</v>
       </c>
       <c r="M15">
         <v>-3.802557567824042</v>
@@ -31115,7 +31115,7 @@
         <v>-1.610198288621323</v>
       </c>
       <c r="P15">
-        <v>-1.10738039689747</v>
+        <v>-1.107380396897511</v>
       </c>
       <c r="Q15">
         <v>-1.174663299953121</v>
@@ -31124,7 +31124,7 @@
         <v>-3.506777925676745</v>
       </c>
       <c r="S15">
-        <v>-3.670537845731613</v>
+        <v>-3.670537845731548</v>
       </c>
     </row>
     <row r="16">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>10.83911617806928</v>
+        <v>10.8391161780693</v>
       </c>
       <c r="C16">
         <v>-25.54670883698141</v>
@@ -31152,10 +31152,10 @@
         <v>-5.022738183846093</v>
       </c>
       <c r="H16">
-        <v>-4.394661814627994</v>
+        <v>-4.394661814628063</v>
       </c>
       <c r="I16">
-        <v>-3.026775626176444</v>
+        <v>-3.026775626176422</v>
       </c>
       <c r="J16">
         <v>-12.94015722890059</v>
@@ -31170,7 +31170,7 @@
         <v>-2.557764111798397</v>
       </c>
       <c r="N16">
-        <v>-1.640225448062521</v>
+        <v>-1.640225448062504</v>
       </c>
       <c r="O16">
         <v>-2.598733425349935</v>
@@ -31198,7 +31198,7 @@
         <v>11.08850705246741</v>
       </c>
       <c r="C17">
-        <v>-30.56173238944319</v>
+        <v>-30.56173238944321</v>
       </c>
       <c r="D17">
         <v>-9.022650281854222</v>
@@ -31222,22 +31222,22 @@
         <v>-17.40482616878052</v>
       </c>
       <c r="K17">
-        <v>-2.904422598762841</v>
+        <v>-2.90442259876289</v>
       </c>
       <c r="L17">
-        <v>7.673613514400567</v>
+        <v>7.673613514400602</v>
       </c>
       <c r="M17">
         <v>-2.080671181204367</v>
       </c>
       <c r="N17">
-        <v>-2.925997511855682</v>
+        <v>-2.925997511855648</v>
       </c>
       <c r="O17">
-        <v>-4.224880695497794</v>
+        <v>-4.22488069549778</v>
       </c>
       <c r="P17">
-        <v>-3.442124029497831</v>
+        <v>-3.442124029497845</v>
       </c>
       <c r="Q17">
         <v>-4.587101571033752</v>
@@ -31246,7 +31246,7 @@
         <v>-6.936937868823173</v>
       </c>
       <c r="S17">
-        <v>-7.400591763754935</v>
+        <v>-7.400591763754918</v>
       </c>
     </row>
     <row r="18">
@@ -31256,13 +31256,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>6.231609525846587</v>
+        <v>6.231609525846604</v>
       </c>
       <c r="C18">
         <v>-29.25245908634126</v>
       </c>
       <c r="D18">
-        <v>-7.780972967821783</v>
+        <v>-7.7809729678218</v>
       </c>
       <c r="E18">
         <v>-19.70687307988793</v>
@@ -31271,7 +31271,7 @@
         <v>-2.722718307719612</v>
       </c>
       <c r="G18">
-        <v>-7.114874424867711</v>
+        <v>-7.1148744248677</v>
       </c>
       <c r="H18">
         <v>-9.044670574527668</v>
@@ -31289,25 +31289,25 @@
         <v>13.7236485126205</v>
       </c>
       <c r="M18">
-        <v>-0.3939622593580469</v>
+        <v>-0.393962259358013</v>
       </c>
       <c r="N18">
-        <v>-2.694350629737933</v>
+        <v>-2.69435062973795</v>
       </c>
       <c r="O18">
         <v>-3.384277341404232</v>
       </c>
       <c r="P18">
-        <v>-3.23576946621488</v>
+        <v>-3.235769466214894</v>
       </c>
       <c r="Q18">
-        <v>-4.450471226916828</v>
+        <v>-4.45047122691686</v>
       </c>
       <c r="R18">
         <v>-6.118733188324448</v>
       </c>
       <c r="S18">
-        <v>-6.635276452968538</v>
+        <v>-6.635276452968555</v>
       </c>
     </row>
     <row r="19">
@@ -31323,10 +31323,10 @@
         <v>-17.67744685927742</v>
       </c>
       <c r="D19">
-        <v>-8.785040602735615</v>
+        <v>-8.785040602735595</v>
       </c>
       <c r="E19">
-        <v>-8.647285995601486</v>
+        <v>-8.647285995601498</v>
       </c>
       <c r="F19">
         <v>-5.762701175300049</v>
@@ -31338,19 +31338,19 @@
         <v>-7.424895641141078</v>
       </c>
       <c r="I19">
-        <v>-9.032857898002998</v>
+        <v>-9.032857898002957</v>
       </c>
       <c r="J19">
-        <v>-1.726801782711014</v>
+        <v>-1.726801782711034</v>
       </c>
       <c r="K19">
         <v>0.8471008269533199</v>
       </c>
       <c r="L19">
-        <v>26.06267383138097</v>
+        <v>26.06267383138101</v>
       </c>
       <c r="M19">
-        <v>0.2603564324028697</v>
+        <v>0.2603564324029037</v>
       </c>
       <c r="N19">
         <v>-4.066295766152005</v>
@@ -31359,16 +31359,16 @@
         <v>-2.242445943903717</v>
       </c>
       <c r="P19">
-        <v>-3.634836132390978</v>
+        <v>-3.634836132390951</v>
       </c>
       <c r="Q19">
         <v>-4.644453110450694</v>
       </c>
       <c r="R19">
-        <v>-5.304723439793023</v>
+        <v>-5.304723439793007</v>
       </c>
       <c r="S19">
-        <v>-5.745176773050596</v>
+        <v>-5.745176773050613</v>
       </c>
     </row>
     <row r="20">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>-3.265153538323016</v>
+        <v>-3.265153538323045</v>
       </c>
       <c r="C20">
         <v>-12.06926542118672</v>
@@ -31396,16 +31396,16 @@
         <v>-7.30380348045653</v>
       </c>
       <c r="H20">
-        <v>-4.046072824073039</v>
+        <v>-4.046072824073003</v>
       </c>
       <c r="I20">
-        <v>-6.900925490667</v>
+        <v>-6.900925490667021</v>
       </c>
       <c r="J20">
         <v>6.583893188327895</v>
       </c>
       <c r="K20">
-        <v>-6.027084235087829</v>
+        <v>-6.027084235087878</v>
       </c>
       <c r="L20">
         <v>15.80494204908936</v>
@@ -31414,7 +31414,7 @@
         <v>-0.02274314776899564</v>
       </c>
       <c r="N20">
-        <v>-4.916470913447606</v>
+        <v>-4.916470913447605</v>
       </c>
       <c r="O20">
         <v>-1.611194896928725</v>
@@ -31426,10 +31426,10 @@
         <v>-3.991180509479215</v>
       </c>
       <c r="R20">
-        <v>-4.183243631742366</v>
+        <v>-4.183243631742399</v>
       </c>
       <c r="S20">
-        <v>-4.39340216931199</v>
+        <v>-4.393402169312008</v>
       </c>
     </row>
     <row r="21">
@@ -31439,13 +31439,13 @@
         </is>
       </c>
       <c r="B21">
-        <v>-4.966425631663985</v>
+        <v>-4.966425631663999</v>
       </c>
       <c r="C21">
-        <v>4.567813401021218</v>
+        <v>4.567813401021254</v>
       </c>
       <c r="D21">
-        <v>-1.293319720200699</v>
+        <v>-1.293319720200678</v>
       </c>
       <c r="E21">
         <v>13.57151723830272</v>
@@ -31457,7 +31457,7 @@
         <v>-3.277091673692241</v>
       </c>
       <c r="H21">
-        <v>0.269533112641722</v>
+        <v>0.2695331126417477</v>
       </c>
       <c r="I21">
         <v>-1.699387716489539</v>
@@ -31466,31 +31466,31 @@
         <v>25.49420026812351</v>
       </c>
       <c r="K21">
-        <v>-9.333205448274899</v>
+        <v>-9.333205448274855</v>
       </c>
       <c r="L21">
-        <v>-0.4899857653060189</v>
+        <v>-0.48998576530604</v>
       </c>
       <c r="M21">
         <v>0.1734048717625322</v>
       </c>
       <c r="N21">
-        <v>-1.785501371479292</v>
+        <v>-1.78550137147931</v>
       </c>
       <c r="O21">
         <v>0.535262220317212</v>
       </c>
       <c r="P21">
-        <v>-1.116981532541094</v>
+        <v>-1.116981532541065</v>
       </c>
       <c r="Q21">
         <v>-1.525926448021208</v>
       </c>
       <c r="R21">
-        <v>-1.005943144064844</v>
+        <v>-1.005943144064827</v>
       </c>
       <c r="S21">
-        <v>-0.8812965025976919</v>
+        <v>-0.8812965025977098</v>
       </c>
     </row>
     <row r="22">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>6.061444159651534</v>
+        <v>6.061444159651504</v>
       </c>
       <c r="C22">
         <v>16.76460705796437</v>
@@ -31515,16 +31515,16 @@
         <v>-8.862706913973327</v>
       </c>
       <c r="G22">
-        <v>-1.084376117319171</v>
+        <v>-1.084376117319183</v>
       </c>
       <c r="H22">
-        <v>0.5574412282792067</v>
+        <v>0.5574412282791679</v>
       </c>
       <c r="I22">
         <v>5.041061570001194</v>
       </c>
       <c r="J22">
-        <v>14.73994494387938</v>
+        <v>14.7399449438794</v>
       </c>
       <c r="K22">
         <v>-12.49978248449705</v>
@@ -31545,13 +31545,13 @@
         <v>0.6585016180137369</v>
       </c>
       <c r="Q22">
-        <v>0.7615652464257577</v>
+        <v>0.761565246425791</v>
       </c>
       <c r="R22">
-        <v>-0.2927990735524236</v>
+        <v>-0.2927990735524404</v>
       </c>
       <c r="S22">
-        <v>-0.04309096284451307</v>
+        <v>-0.04309096284449487</v>
       </c>
     </row>
     <row r="23">
@@ -31567,10 +31567,10 @@
         <v>8.552880689373534</v>
       </c>
       <c r="D23">
-        <v>4.246845556526367</v>
+        <v>4.246845556526345</v>
       </c>
       <c r="E23">
-        <v>8.451730236994802</v>
+        <v>8.451730236994816</v>
       </c>
       <c r="F23">
         <v>-1.879974353667043</v>
@@ -31585,7 +31585,7 @@
         <v>2.674752515730396</v>
       </c>
       <c r="J23">
-        <v>15.7253793607209</v>
+        <v>15.72537936072092</v>
       </c>
       <c r="K23">
         <v>-6.241959271310582</v>
@@ -31594,22 +31594,22 @@
         <v>-21.34817266379697</v>
       </c>
       <c r="M23">
-        <v>-1.87605181437839</v>
+        <v>-1.876051814378423</v>
       </c>
       <c r="N23">
-        <v>2.791908902994493</v>
+        <v>2.791908902994475</v>
       </c>
       <c r="O23">
-        <v>0.3233680537769711</v>
+        <v>0.3233680537770012</v>
       </c>
       <c r="P23">
-        <v>3.039899382615596</v>
+        <v>3.039899382615582</v>
       </c>
       <c r="Q23">
-        <v>2.602372312205048</v>
+        <v>2.602372312205081</v>
       </c>
       <c r="R23">
-        <v>0.9784736590393858</v>
+        <v>0.9784736590393687</v>
       </c>
       <c r="S23">
         <v>1.140065688032669</v>
@@ -31622,16 +31622,16 @@
         </is>
       </c>
       <c r="B24">
-        <v>13.02126576674265</v>
+        <v>13.02126576674268</v>
       </c>
       <c r="C24">
-        <v>28.41710473314554</v>
+        <v>28.41710473314559</v>
       </c>
       <c r="D24">
-        <v>4.974410271586862</v>
+        <v>4.974410271586841</v>
       </c>
       <c r="E24">
-        <v>-5.639734132856093</v>
+        <v>-5.639734132856106</v>
       </c>
       <c r="F24">
         <v>2.309731789349656</v>
@@ -31649,7 +31649,7 @@
         <v>11.52241890028544</v>
       </c>
       <c r="K24">
-        <v>-0.208707609454256</v>
+        <v>-0.2087076094542034</v>
       </c>
       <c r="L24">
         <v>-22.43164700608965</v>
@@ -31658,7 +31658,7 @@
         <v>-2.185288952305952</v>
       </c>
       <c r="N24">
-        <v>5.822770650824619</v>
+        <v>5.8227706508246</v>
       </c>
       <c r="O24">
         <v>0.869970900328904</v>
@@ -31670,10 +31670,10 @@
         <v>3.376672595976843</v>
       </c>
       <c r="R24">
-        <v>1.583707486140418</v>
+        <v>1.583707486140487</v>
       </c>
       <c r="S24">
-        <v>1.677283446155434</v>
+        <v>1.677283446155453</v>
       </c>
     </row>
     <row r="25">
@@ -31683,13 +31683,13 @@
         </is>
       </c>
       <c r="B25">
-        <v>15.66526029314124</v>
+        <v>15.66526029314126</v>
       </c>
       <c r="C25">
         <v>7.220919968937803</v>
       </c>
       <c r="D25">
-        <v>4.485054518154171</v>
+        <v>4.485054518154149</v>
       </c>
       <c r="E25">
         <v>-13.19955513748346</v>
@@ -31701,10 +31701,10 @@
         <v>4.785201569686046</v>
       </c>
       <c r="H25">
-        <v>4.537103615872423</v>
+        <v>4.537103615872397</v>
       </c>
       <c r="I25">
-        <v>-4.069007266875873</v>
+        <v>-4.069007266875907</v>
       </c>
       <c r="J25">
         <v>1.593955771463448</v>
@@ -31719,19 +31719,19 @@
         <v>-1.824511749330858</v>
       </c>
       <c r="N25">
-        <v>2.195791499553752</v>
+        <v>2.195791499553734</v>
       </c>
       <c r="O25">
         <v>0.6011429611272533</v>
       </c>
       <c r="P25">
-        <v>3.23591033953529</v>
+        <v>3.235910339535305</v>
       </c>
       <c r="Q25">
         <v>3.668765724696098</v>
       </c>
       <c r="R25">
-        <v>1.55956507714997</v>
+        <v>1.559565077149953</v>
       </c>
       <c r="S25">
         <v>1.361845657917049</v>
@@ -31744,13 +31744,13 @@
         </is>
       </c>
       <c r="B26">
-        <v>5.110473487265427</v>
+        <v>5.110473487265442</v>
       </c>
       <c r="C26">
         <v>-11.78922512140011</v>
       </c>
       <c r="D26">
-        <v>4.381599895704426</v>
+        <v>4.381599895704446</v>
       </c>
       <c r="E26">
         <v>-15.96430388301283</v>
@@ -31759,16 +31759,16 @@
         <v>3.936757390661039</v>
       </c>
       <c r="G26">
-        <v>3.615998960057109</v>
+        <v>3.615998960057096</v>
       </c>
       <c r="H26">
-        <v>6.896070428360034</v>
+        <v>6.896070428360075</v>
       </c>
       <c r="I26">
         <v>-6.793490813313515</v>
       </c>
       <c r="J26">
-        <v>4.82311577110687</v>
+        <v>4.823115771106834</v>
       </c>
       <c r="K26">
         <v>17.06020928735269</v>
@@ -31786,13 +31786,13 @@
         <v>1.981264040697067</v>
       </c>
       <c r="P26">
-        <v>2.711459686947433</v>
+        <v>2.711459686947447</v>
       </c>
       <c r="Q26">
         <v>2.733307171158775</v>
       </c>
       <c r="R26">
-        <v>2.383154157885756</v>
+        <v>2.383154157885773</v>
       </c>
       <c r="S26">
         <v>1.978198547571901</v>
@@ -31805,10 +31805,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-3.093775336370434</v>
+        <v>-3.093775336370407</v>
       </c>
       <c r="C27">
-        <v>-7.631720264747964</v>
+        <v>-7.631720264747933</v>
       </c>
       <c r="D27">
         <v>-0.1850091710388544</v>
@@ -31829,7 +31829,7 @@
         <v>-3.346844877718767</v>
       </c>
       <c r="J27">
-        <v>-3.646073411270979</v>
+        <v>-3.646073411270996</v>
       </c>
       <c r="K27">
         <v>12.29255450429801</v>
@@ -31838,19 +31838,19 @@
         <v>12.6561433277163</v>
       </c>
       <c r="M27">
-        <v>2.037061357658175</v>
+        <v>2.037061357658209</v>
       </c>
       <c r="N27">
-        <v>-1.032967186814855</v>
+        <v>-1.032967186814838</v>
       </c>
       <c r="O27">
-        <v>2.734548927438308</v>
+        <v>2.734548927438277</v>
       </c>
       <c r="P27">
-        <v>0.08485960448793498</v>
+        <v>0.08485960448797721</v>
       </c>
       <c r="Q27">
-        <v>0.5920602707093582</v>
+        <v>0.5920602707093257</v>
       </c>
       <c r="R27">
         <v>1.483169268307323</v>
@@ -31869,13 +31869,13 @@
         <v>-1.314244744151617</v>
       </c>
       <c r="C28">
-        <v>-12.42121282302656</v>
+        <v>-12.42121282302659</v>
       </c>
       <c r="D28">
-        <v>2.234551444694284</v>
+        <v>2.234551444694305</v>
       </c>
       <c r="E28">
-        <v>-7.877366383493246</v>
+        <v>-7.877366383493247</v>
       </c>
       <c r="F28">
         <v>-4.249740907235857</v>
@@ -31896,7 +31896,7 @@
         <v>17.08775672972295</v>
       </c>
       <c r="L28">
-        <v>22.63601470021466</v>
+        <v>22.63601470021468</v>
       </c>
       <c r="M28">
         <v>3.834441231262681</v>
@@ -31914,7 +31914,7 @@
         <v>2.331296064351911</v>
       </c>
       <c r="R28">
-        <v>3.248519114955916</v>
+        <v>3.248519114955881</v>
       </c>
       <c r="S28">
         <v>2.772948331833576</v>
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="B29">
-        <v>-1.663702017627633</v>
+        <v>-1.66370201762762</v>
       </c>
       <c r="C29">
         <v>12.02669897045988</v>
       </c>
       <c r="D29">
-        <v>3.466882235299245</v>
+        <v>3.466882235299225</v>
       </c>
       <c r="E29">
         <v>-0.6030397602905438</v>
@@ -31948,7 +31948,7 @@
         <v>6.908823881866851</v>
       </c>
       <c r="I29">
-        <v>3.220353671094832</v>
+        <v>3.22035367109487</v>
       </c>
       <c r="J29">
         <v>-11.24563411222854</v>
@@ -31957,7 +31957,7 @@
         <v>18.06683373486042</v>
       </c>
       <c r="L29">
-        <v>7.15068278362598</v>
+        <v>7.150682783626002</v>
       </c>
       <c r="M29">
         <v>3.284194050683207</v>
@@ -31969,13 +31969,13 @@
         <v>3.039902951916872</v>
       </c>
       <c r="P29">
-        <v>2.248577049025331</v>
+        <v>2.248577049025317</v>
       </c>
       <c r="Q29">
         <v>2.475590589138627</v>
       </c>
       <c r="R29">
-        <v>3.475226911220611</v>
+        <v>3.475226911220644</v>
       </c>
       <c r="S29">
         <v>3.118443714885646</v>
@@ -31994,7 +31994,7 @@
         <v>48.26953658588875</v>
       </c>
       <c r="D30">
-        <v>3.424646801969232</v>
+        <v>3.424646801969212</v>
       </c>
       <c r="E30">
         <v>4.134684657075509</v>
@@ -32003,7 +32003,7 @@
         <v>-6.324546691548471</v>
       </c>
       <c r="G30">
-        <v>1.788889401732681</v>
+        <v>1.78888940173273</v>
       </c>
       <c r="H30">
         <v>5.641267413468411</v>
@@ -32012,7 +32012,7 @@
         <v>5.046732825438305</v>
       </c>
       <c r="J30">
-        <v>-16.13088497975938</v>
+        <v>-16.13088497975936</v>
       </c>
       <c r="K30">
         <v>11.57050132812486</v>
@@ -32021,7 +32021,7 @@
         <v>3.279968826593402</v>
       </c>
       <c r="M30">
-        <v>0.3129430693944721</v>
+        <v>0.3129430693944379</v>
       </c>
       <c r="N30">
         <v>-3.857330778948302</v>
@@ -32030,7 +32030,7 @@
         <v>1.369042150138182</v>
       </c>
       <c r="P30">
-        <v>1.34480623536522</v>
+        <v>1.344806235365206</v>
       </c>
       <c r="Q30">
         <v>1.650020138150249</v>
@@ -32049,13 +32049,13 @@
         </is>
       </c>
       <c r="B31">
-        <v>2.842003756467673</v>
+        <v>2.842003756467645</v>
       </c>
       <c r="C31">
-        <v>50.18948731667249</v>
+        <v>50.18948731667244</v>
       </c>
       <c r="D31">
-        <v>8.862317509248122</v>
+        <v>8.862317509248143</v>
       </c>
       <c r="E31">
         <v>15.49101678118223</v>
@@ -32082,16 +32082,16 @@
         <v>-2.589989532850438</v>
       </c>
       <c r="M31">
-        <v>-1.864838152603703</v>
+        <v>-1.864838152603736</v>
       </c>
       <c r="N31">
-        <v>-4.583342703611448</v>
+        <v>-4.58334270361143</v>
       </c>
       <c r="O31">
-        <v>-0.3922742588398327</v>
+        <v>-0.3922742588398181</v>
       </c>
       <c r="P31">
-        <v>2.824244124809574</v>
+        <v>2.824244124809531</v>
       </c>
       <c r="Q31">
         <v>2.984228548200778</v>
@@ -32119,7 +32119,7 @@
         <v>4.773573657279867</v>
       </c>
       <c r="E32">
-        <v>15.42757763796581</v>
+        <v>15.42757763796583</v>
       </c>
       <c r="F32">
         <v>-1.418818754573815</v>
@@ -32140,7 +32140,7 @@
         <v>8.366291420448494</v>
       </c>
       <c r="L32">
-        <v>-1.741198351691234</v>
+        <v>-1.741198351691254</v>
       </c>
       <c r="M32">
         <v>-4.024556559141041</v>
@@ -32149,7 +32149,7 @@
         <v>-5.050288090769233</v>
       </c>
       <c r="O32">
-        <v>-2.82992209857529</v>
+        <v>-2.829922098575304</v>
       </c>
       <c r="P32">
         <v>-0.3995336065189795</v>
@@ -32171,13 +32171,13 @@
         </is>
       </c>
       <c r="B33">
-        <v>2.35272693547218</v>
+        <v>2.352726935472166</v>
       </c>
       <c r="C33">
         <v>-8.271136070590744</v>
       </c>
       <c r="D33">
-        <v>-0.3069601443039631</v>
+        <v>-0.3069601443039438</v>
       </c>
       <c r="E33">
         <v>23.02332330897759</v>
@@ -32201,13 +32201,13 @@
         <v>8.712065267824785</v>
       </c>
       <c r="L33">
-        <v>4.585037510011849</v>
+        <v>4.585037510011826</v>
       </c>
       <c r="M33">
         <v>-3.885214950027712</v>
       </c>
       <c r="N33">
-        <v>-5.397195707871036</v>
+        <v>-5.397195707871018</v>
       </c>
       <c r="O33">
         <v>-3.721429486141384</v>
@@ -32216,10 +32216,10 @@
         <v>-2.003993676353578</v>
       </c>
       <c r="Q33">
-        <v>-1.702829828007715</v>
+        <v>-1.702829828007683</v>
       </c>
       <c r="R33">
-        <v>-2.369796797822501</v>
+        <v>-2.369796797822533</v>
       </c>
       <c r="S33">
         <v>-2.792079842667434</v>
@@ -32235,7 +32235,7 @@
         <v>4.75255349701209</v>
       </c>
       <c r="C34">
-        <v>-22.84094202783752</v>
+        <v>-22.84094202783749</v>
       </c>
       <c r="D34">
         <v>-1.031956268259862</v>
@@ -32247,25 +32247,25 @@
         <v>1.115382570921514</v>
       </c>
       <c r="G34">
-        <v>0.2238081790081216</v>
+        <v>0.223808179008074</v>
       </c>
       <c r="H34">
         <v>-2.557557261935745</v>
       </c>
       <c r="I34">
-        <v>-15.65393788228083</v>
+        <v>-15.65393788228079</v>
       </c>
       <c r="J34">
-        <v>-7.615377361816628</v>
+        <v>-7.615377361816607</v>
       </c>
       <c r="K34">
         <v>14.79824676329998</v>
       </c>
       <c r="L34">
-        <v>18.35033952407631</v>
+        <v>18.35033952407633</v>
       </c>
       <c r="M34">
-        <v>-0.9247466790750647</v>
+        <v>-0.9247466790750307</v>
       </c>
       <c r="N34">
         <v>-4.605855444413402</v>
@@ -32280,10 +32280,10 @@
         <v>-0.8784893453238819</v>
       </c>
       <c r="R34">
-        <v>-1.770468707854004</v>
+        <v>-1.770468707853972</v>
       </c>
       <c r="S34">
-        <v>-2.383642744943147</v>
+        <v>-2.383642744943182</v>
       </c>
     </row>
     <row r="35">
@@ -32299,7 +32299,7 @@
         <v>-13.25158140569845</v>
       </c>
       <c r="D35">
-        <v>-3.655296970600252</v>
+        <v>-3.655296970600269</v>
       </c>
       <c r="E35">
         <v>26.56916084395296</v>
@@ -32308,7 +32308,7 @@
         <v>7.130492709678417</v>
       </c>
       <c r="G35">
-        <v>-0.3913373474139444</v>
+        <v>-0.391337347413956</v>
       </c>
       <c r="H35">
         <v>1.546475111645455</v>
@@ -32326,16 +32326,16 @@
         <v>27.43767348300194</v>
       </c>
       <c r="M35">
-        <v>2.888954311358845</v>
+        <v>2.88895431135888</v>
       </c>
       <c r="N35">
-        <v>0.710036644122335</v>
+        <v>0.7100366441223163</v>
       </c>
       <c r="O35">
-        <v>2.982804007980069</v>
+        <v>2.982804007980054</v>
       </c>
       <c r="P35">
-        <v>-0.8540988140304615</v>
+        <v>-0.854098814030448</v>
       </c>
       <c r="Q35">
         <v>-2.973597628370911</v>
@@ -32378,7 +32378,7 @@
         <v>-6.396114006492566</v>
       </c>
       <c r="J36">
-        <v>1.383933941889687</v>
+        <v>1.383933941889709</v>
       </c>
       <c r="K36">
         <v>13.16181011355198</v>
@@ -32390,10 +32390,10 @@
         <v>7.025865540228758</v>
       </c>
       <c r="N36">
-        <v>5.295928809173413</v>
+        <v>5.295928809173394</v>
       </c>
       <c r="O36">
-        <v>8.636883307307809</v>
+        <v>8.636883307307825</v>
       </c>
       <c r="P36">
         <v>4.108356094029888</v>
@@ -32405,7 +32405,7 @@
         <v>6.656162008970795</v>
       </c>
       <c r="S36">
-        <v>5.42331620024316</v>
+        <v>5.423316200243142</v>
       </c>
     </row>
     <row r="37">
@@ -32427,7 +32427,7 @@
         <v>8.044644917140797</v>
       </c>
       <c r="F37">
-        <v>17.25542718960183</v>
+        <v>17.25542718960179</v>
       </c>
       <c r="G37">
         <v>13.56506028253826</v>
@@ -32460,7 +32460,7 @@
         <v>7.23969944978256</v>
       </c>
       <c r="Q37">
-        <v>4.568327410179251</v>
+        <v>4.568327410179219</v>
       </c>
       <c r="R37">
         <v>12.15826845414494</v>
@@ -32479,7 +32479,7 @@
         <v>-28.37410384713858</v>
       </c>
       <c r="C38">
-        <v>70.10966581557201</v>
+        <v>70.10966581557194</v>
       </c>
       <c r="D38">
         <v>16.49562449190169</v>
@@ -32491,28 +32491,28 @@
         <v>25.1927709094417</v>
       </c>
       <c r="G38">
-        <v>18.21126205386463</v>
+        <v>18.21126205386464</v>
       </c>
       <c r="H38">
-        <v>10.44199150351286</v>
+        <v>10.44199150351291</v>
       </c>
       <c r="I38">
-        <v>9.648128700662937</v>
+        <v>9.648128700662893</v>
       </c>
       <c r="J38">
-        <v>-0.09860492726931014</v>
+        <v>-0.09860492726933198</v>
       </c>
       <c r="K38">
         <v>-28.80976280405089</v>
       </c>
       <c r="L38">
-        <v>46.65477215214224</v>
+        <v>46.65477215214221</v>
       </c>
       <c r="M38">
         <v>8.450301873478089</v>
       </c>
       <c r="N38">
-        <v>6.086162750789395</v>
+        <v>6.086162750789414</v>
       </c>
       <c r="O38">
         <v>10.30892484904751</v>
@@ -32524,10 +32524,10 @@
         <v>5.494728946293984</v>
       </c>
       <c r="R38">
-        <v>12.56795688907155</v>
+        <v>12.56795688907153</v>
       </c>
       <c r="S38">
-        <v>12.9375631583912</v>
+        <v>12.93756315839125</v>
       </c>
     </row>
     <row r="39">
@@ -32543,7 +32543,7 @@
         <v>25.95690284010014</v>
       </c>
       <c r="D39">
-        <v>18.69277500773038</v>
+        <v>18.69277500773035</v>
       </c>
       <c r="E39">
         <v>-8.755502369445825</v>
@@ -32552,7 +32552,7 @@
         <v>15.87985727024995</v>
       </c>
       <c r="G39">
-        <v>16.89307180092382</v>
+        <v>16.89307180092383</v>
       </c>
       <c r="H39">
         <v>2.523400615133084</v>
@@ -32561,7 +32561,7 @@
         <v>11.38663284251114</v>
       </c>
       <c r="J39">
-        <v>-8.704056818863414</v>
+        <v>-8.704056818863384</v>
       </c>
       <c r="K39">
         <v>-43.38870365621404</v>
@@ -32570,7 +32570,7 @@
         <v>36.48252681616386</v>
       </c>
       <c r="M39">
-        <v>4.576137987836113</v>
+        <v>4.576137987836078</v>
       </c>
       <c r="N39">
         <v>-1.737736495630172</v>
@@ -32613,7 +32613,7 @@
         <v>8.489579616255771</v>
       </c>
       <c r="G40">
-        <v>9.127276358173892</v>
+        <v>9.127276358173916</v>
       </c>
       <c r="H40">
         <v>-6.758201108217469</v>
@@ -32622,19 +32622,19 @@
         <v>8.938904588800444</v>
       </c>
       <c r="J40">
-        <v>-5.17730888647083</v>
+        <v>-5.17730888647085</v>
       </c>
       <c r="K40">
         <v>-42.92787549169718</v>
       </c>
       <c r="L40">
-        <v>16.54120751578522</v>
+        <v>16.54120751578523</v>
       </c>
       <c r="M40">
-        <v>0.01335901714651821</v>
+        <v>0.01335901714656171</v>
       </c>
       <c r="N40">
-        <v>-7.39511949100755</v>
+        <v>-7.395119491007497</v>
       </c>
       <c r="O40">
         <v>-4.727509145805318</v>
@@ -32649,7 +32649,7 @@
         <v>0.2375007031319486</v>
       </c>
       <c r="S40">
-        <v>2.458704092941964</v>
+        <v>2.458704092941981</v>
       </c>
     </row>
     <row r="41">
@@ -32665,13 +32665,13 @@
         <v>-45.68522734725858</v>
       </c>
       <c r="D41">
-        <v>1.365102007725509</v>
+        <v>1.365102007725492</v>
       </c>
       <c r="E41">
         <v>-4.257559618007805</v>
       </c>
       <c r="F41">
-        <v>-0.174581139826279</v>
+        <v>-0.1745811398262415</v>
       </c>
       <c r="G41">
         <v>-0.6274352498211231</v>
@@ -32698,7 +32698,7 @@
         <v>-9.931414105862805</v>
       </c>
       <c r="O41">
-        <v>-7.925231009913347</v>
+        <v>-7.925231009913321</v>
       </c>
       <c r="P41">
         <v>-2.263498857759484</v>
@@ -32707,7 +32707,7 @@
         <v>0.264544287338248</v>
       </c>
       <c r="R41">
-        <v>-4.955611956070397</v>
+        <v>-4.955611956070368</v>
       </c>
       <c r="S41">
         <v>-3.10339648031509</v>
@@ -32735,10 +32735,10 @@
         <v>-9.257640864993959</v>
       </c>
       <c r="G42">
-        <v>-7.73866947195977</v>
+        <v>-7.738669471959791</v>
       </c>
       <c r="H42">
-        <v>-8.581210247204661</v>
+        <v>-8.5812102472047</v>
       </c>
       <c r="I42">
         <v>4.916335758819951</v>
@@ -32756,7 +32756,7 @@
         <v>-4.104483287850149</v>
       </c>
       <c r="N42">
-        <v>-8.444448727194432</v>
+        <v>-8.44444872719445</v>
       </c>
       <c r="O42">
         <v>-7.777795319081403</v>
@@ -32768,10 +32768,10 @@
         <v>-3.475441872207543</v>
       </c>
       <c r="R42">
-        <v>-7.127210065768148</v>
+        <v>-7.127210065768175</v>
       </c>
       <c r="S42">
-        <v>-5.897768089670301</v>
+        <v>-5.897768089670286</v>
       </c>
     </row>
     <row r="43">
@@ -32787,7 +32787,7 @@
         <v>-34.53256187733369</v>
       </c>
       <c r="D43">
-        <v>-10.94784184757771</v>
+        <v>-10.9478418475777</v>
       </c>
       <c r="E43">
         <v>9.76377807594297</v>
@@ -32799,13 +32799,13 @@
         <v>-10.12550077785758</v>
       </c>
       <c r="H43">
-        <v>-4.506357699119374</v>
+        <v>-4.506357699119341</v>
       </c>
       <c r="I43">
         <v>-1.875944176003371</v>
       </c>
       <c r="J43">
-        <v>13.71313595406082</v>
+        <v>13.71313595406078</v>
       </c>
       <c r="K43">
         <v>11.23179458919881</v>
@@ -32814,22 +32814,22 @@
         <v>-44.48571845388035</v>
       </c>
       <c r="M43">
-        <v>-4.010084855790876</v>
+        <v>-4.010084855790844</v>
       </c>
       <c r="N43">
         <v>-4.699702866511419</v>
       </c>
       <c r="O43">
-        <v>-5.418016474929447</v>
+        <v>-5.418016474929476</v>
       </c>
       <c r="P43">
         <v>-11.36554852555639</v>
       </c>
       <c r="Q43">
-        <v>-11.63665624002035</v>
+        <v>-11.63665624002038</v>
       </c>
       <c r="R43">
-        <v>-6.810346571310078</v>
+        <v>-6.810346571310108</v>
       </c>
       <c r="S43">
         <v>-6.452923244137686</v>
@@ -32848,7 +32848,7 @@
         <v>-12.27043236095111</v>
       </c>
       <c r="D44">
-        <v>-13.62080452971168</v>
+        <v>-13.62080452971166</v>
       </c>
       <c r="E44">
         <v>20.008727920638</v>
@@ -32857,7 +32857,7 @@
         <v>-5.792583412954259</v>
       </c>
       <c r="G44">
-        <v>-10.57576335271089</v>
+        <v>-10.57576335271092</v>
       </c>
       <c r="H44">
         <v>1.423105337994796</v>
@@ -32875,10 +32875,10 @@
         <v>-47.33073397965794</v>
       </c>
       <c r="M44">
-        <v>-3.026378465185364</v>
+        <v>-3.026378465185406</v>
       </c>
       <c r="N44">
-        <v>-0.2452308890570956</v>
+        <v>-0.2452308890571149</v>
       </c>
       <c r="O44">
         <v>-2.61277588870165</v>
@@ -32887,7 +32887,7 @@
         <v>-9.307879461814258</v>
       </c>
       <c r="Q44">
-        <v>-9.829886550143494</v>
+        <v>-9.829886550143462</v>
       </c>
       <c r="R44">
         <v>-4.863959326906434</v>
@@ -32909,7 +32909,7 @@
         <v>30.55081156045603</v>
       </c>
       <c r="D45">
-        <v>-13.57903593174674</v>
+        <v>-13.57903593174673</v>
       </c>
       <c r="E45">
         <v>21.77153212581527</v>
@@ -32936,13 +32936,13 @@
         <v>-44.07436253117159</v>
       </c>
       <c r="M45">
-        <v>0.2710674519876883</v>
+        <v>0.2710674519876662</v>
       </c>
       <c r="N45">
-        <v>2.089367775478981</v>
+        <v>2.089367775478961</v>
       </c>
       <c r="O45">
-        <v>-1.539029348788454</v>
+        <v>-1.539029348788483</v>
       </c>
       <c r="P45">
         <v>-8.671138553213423</v>
@@ -32951,7 +32951,7 @@
         <v>-9.442624224338253</v>
       </c>
       <c r="R45">
-        <v>-3.944543612711023</v>
+        <v>-3.944543612711022</v>
       </c>
       <c r="S45">
         <v>-3.899172268651174</v>
@@ -32979,7 +32979,7 @@
         <v>-4.369949152119907</v>
       </c>
       <c r="G46">
-        <v>-11.04826743803987</v>
+        <v>-11.04826743803986</v>
       </c>
       <c r="H46">
         <v>4.209036818566594</v>
@@ -32988,7 +32988,7 @@
         <v>-6.997320737372167</v>
       </c>
       <c r="J46">
-        <v>1.799394048473939</v>
+        <v>1.799394048473959</v>
       </c>
       <c r="K46">
         <v>-0.5302505273481218</v>
@@ -33000,10 +33000,10 @@
         <v>0.06142138533402332</v>
       </c>
       <c r="N46">
-        <v>2.668410204556909</v>
+        <v>2.668410204556929</v>
       </c>
       <c r="O46">
-        <v>-0.7392319898545618</v>
+        <v>-0.7392319898545472</v>
       </c>
       <c r="P46">
         <v>-7.094994672274638</v>
@@ -33012,10 +33012,10 @@
         <v>-8.061637327934632</v>
       </c>
       <c r="R46">
-        <v>-4.1996429144199</v>
+        <v>-4.199642914419885</v>
       </c>
       <c r="S46">
-        <v>-4.177535944457095</v>
+        <v>-4.177535944457111</v>
       </c>
     </row>
     <row r="47">
@@ -33043,7 +33043,7 @@
         <v>-12.32589973179785</v>
       </c>
       <c r="H47">
-        <v>3.206551279294387</v>
+        <v>3.206551279294352</v>
       </c>
       <c r="I47">
         <v>1.620915827535572</v>
@@ -33058,22 +33058,22 @@
         <v>-7.047167746244788</v>
       </c>
       <c r="M47">
-        <v>1.273081912657632</v>
+        <v>1.273081912657598</v>
       </c>
       <c r="N47">
-        <v>4.149489449239853</v>
+        <v>4.149489449239834</v>
       </c>
       <c r="O47">
-        <v>0.6918614753361096</v>
+        <v>0.6918614753361246</v>
       </c>
       <c r="P47">
         <v>-0.9596692707403071</v>
       </c>
       <c r="Q47">
-        <v>-0.814787152923691</v>
+        <v>-0.814787152923658</v>
       </c>
       <c r="R47">
-        <v>-3.884146285477528</v>
+        <v>-3.88414628547745</v>
       </c>
       <c r="S47">
         <v>-3.967109618518587</v>
@@ -33092,7 +33092,7 @@
         <v>12.53121668722699</v>
       </c>
       <c r="D48">
-        <v>-11.31687830546762</v>
+        <v>-11.31687830546764</v>
       </c>
       <c r="E48">
         <v>11.58677081046916</v>
@@ -33101,13 +33101,13 @@
         <v>-9.30758217242308</v>
       </c>
       <c r="G48">
-        <v>-10.26011912899827</v>
+        <v>-10.26011912899826</v>
       </c>
       <c r="H48">
         <v>3.255409299236467</v>
       </c>
       <c r="I48">
-        <v>4.154774507008834</v>
+        <v>4.154774507008872</v>
       </c>
       <c r="J48">
         <v>-11.41811435706971</v>
@@ -33119,10 +33119,10 @@
         <v>8.053660273007186</v>
       </c>
       <c r="M48">
-        <v>1.550484154746854</v>
+        <v>1.550484154746831</v>
       </c>
       <c r="N48">
-        <v>3.874740685078453</v>
+        <v>3.874740685078432</v>
       </c>
       <c r="O48">
         <v>1.478688917685709</v>
@@ -33131,7 +33131,7 @@
         <v>0.6677216692785053</v>
       </c>
       <c r="Q48">
-        <v>0.4094094732786453</v>
+        <v>0.4094094732786118</v>
       </c>
       <c r="R48">
         <v>-2.870524940030732</v>
@@ -33150,7 +33150,7 @@
         <v>26.20345024252235</v>
       </c>
       <c r="C49">
-        <v>-12.40751848977632</v>
+        <v>-12.40751848977635</v>
       </c>
       <c r="D49">
         <v>-8.504994380559216</v>
@@ -33180,10 +33180,10 @@
         <v>15.05731640642726</v>
       </c>
       <c r="M49">
-        <v>-0.1786915069646016</v>
+        <v>-0.1786915069645796</v>
       </c>
       <c r="N49">
-        <v>3.682991349338118</v>
+        <v>3.682991349338139</v>
       </c>
       <c r="O49">
         <v>1.57016832129948</v>
@@ -33195,7 +33195,7 @@
         <v>0.8432824543654381</v>
       </c>
       <c r="R49">
-        <v>-2.130004405315185</v>
+        <v>-2.130004405315216</v>
       </c>
       <c r="S49">
         <v>-2.442743178317361</v>
@@ -33226,13 +33226,13 @@
         <v>-1.650562028013306</v>
       </c>
       <c r="H50">
-        <v>2.207817450142862</v>
+        <v>2.207817450142817</v>
       </c>
       <c r="I50">
         <v>6.507794901276026</v>
       </c>
       <c r="J50">
-        <v>-6.415968832120827</v>
+        <v>-6.415968832120846</v>
       </c>
       <c r="K50">
         <v>-2.889998988970977</v>
@@ -33241,13 +33241,13 @@
         <v>2.964002081709281</v>
       </c>
       <c r="M50">
-        <v>0.8750086092275161</v>
+        <v>0.8750086092274719</v>
       </c>
       <c r="N50">
-        <v>3.764388336509243</v>
+        <v>3.764388336509223</v>
       </c>
       <c r="O50">
-        <v>1.594835168945909</v>
+        <v>1.594835168945893</v>
       </c>
       <c r="P50">
         <v>4.2333469004217</v>
@@ -33256,10 +33256,10 @@
         <v>4.58035755679051</v>
       </c>
       <c r="R50">
-        <v>0.2263955404928475</v>
+        <v>0.2263955404928312</v>
       </c>
       <c r="S50">
-        <v>-0.06529780798310428</v>
+        <v>-0.06529780798312181</v>
       </c>
     </row>
     <row r="51">
@@ -33287,7 +33287,7 @@
         <v>2.610507957086529</v>
       </c>
       <c r="H51">
-        <v>2.929308789779478</v>
+        <v>2.929308789779434</v>
       </c>
       <c r="I51">
         <v>-0.5920678587749287</v>
@@ -33299,25 +33299,25 @@
         <v>6.003955497851646</v>
       </c>
       <c r="L51">
-        <v>-5.22112868734035</v>
+        <v>-5.221128687340364</v>
       </c>
       <c r="M51">
         <v>1.800339948508204</v>
       </c>
       <c r="N51">
-        <v>1.520964236574965</v>
+        <v>1.520964236574984</v>
       </c>
       <c r="O51">
-        <v>1.471708319648595</v>
+        <v>1.471708319648624</v>
       </c>
       <c r="P51">
-        <v>4.840597594367705</v>
+        <v>4.840597594367734</v>
       </c>
       <c r="Q51">
         <v>6.158149475482328</v>
       </c>
       <c r="R51">
-        <v>1.833953022875312</v>
+        <v>1.833953022875262</v>
       </c>
       <c r="S51">
         <v>1.50618288445896</v>
@@ -33330,13 +33330,13 @@
         </is>
       </c>
       <c r="B52">
-        <v>41.6519713367517</v>
+        <v>41.65197133675174</v>
       </c>
       <c r="C52">
         <v>19.64509298375532</v>
       </c>
       <c r="D52">
-        <v>-0.9577666434609051</v>
+        <v>-0.9577666434608836</v>
       </c>
       <c r="E52">
         <v>27.02522712263606</v>
@@ -33345,13 +33345,13 @@
         <v>2.562109818102557</v>
       </c>
       <c r="G52">
-        <v>1.862769598542071</v>
+        <v>1.862769598542058</v>
       </c>
       <c r="H52">
         <v>0.3496655725066289</v>
       </c>
       <c r="I52">
-        <v>-5.576890103112532</v>
+        <v>-5.576890103112604</v>
       </c>
       <c r="J52">
         <v>6.722067113677983</v>
@@ -33363,7 +33363,7 @@
         <v>-8.924357251041753</v>
       </c>
       <c r="M52">
-        <v>3.396891249803134</v>
+        <v>3.396891249803157</v>
       </c>
       <c r="N52">
         <v>-1.781289739229062</v>
@@ -33375,7 +33375,7 @@
         <v>4.159898679307741</v>
       </c>
       <c r="Q52">
-        <v>5.670457729589992</v>
+        <v>5.670457729589975</v>
       </c>
       <c r="R52">
         <v>1.349301333140973</v>
@@ -33394,7 +33394,7 @@
         <v>48.35943281276107</v>
       </c>
       <c r="C53">
-        <v>31.2361118232809</v>
+        <v>31.23611182328095</v>
       </c>
       <c r="D53">
         <v>-2.405179993248676</v>
@@ -33415,7 +33415,7 @@
         <v>-7.815243891679319</v>
       </c>
       <c r="J53">
-        <v>3.01831585707503</v>
+        <v>3.018315857075009</v>
       </c>
       <c r="K53">
         <v>24.84464826054441</v>
@@ -33436,7 +33436,7 @@
         <v>4.204316711651128</v>
       </c>
       <c r="Q53">
-        <v>5.831773786990883</v>
+        <v>5.831773786990866</v>
       </c>
       <c r="R53">
         <v>0.9355684153035604</v>
@@ -33455,22 +33455,22 @@
         <v>31.68271411667341</v>
       </c>
       <c r="C54">
-        <v>50.14280226211063</v>
+        <v>50.14280226211066</v>
       </c>
       <c r="D54">
-        <v>-5.094607524042891</v>
+        <v>-5.094607524042881</v>
       </c>
       <c r="E54">
         <v>1.524254336839418</v>
       </c>
       <c r="F54">
-        <v>7.653732442799894</v>
+        <v>7.653732442799937</v>
       </c>
       <c r="G54">
-        <v>-1.915541496769691</v>
+        <v>-1.915541496769667</v>
       </c>
       <c r="H54">
-        <v>1.066133549330774</v>
+        <v>1.066133549330818</v>
       </c>
       <c r="I54">
         <v>-10.54140795483536</v>
@@ -33485,13 +33485,13 @@
         <v>-5.520697870866952</v>
       </c>
       <c r="M54">
-        <v>2.688228009218914</v>
+        <v>2.688228009218959</v>
       </c>
       <c r="N54">
         <v>-6.615519147328513</v>
       </c>
       <c r="O54">
-        <v>-0.6956377431694736</v>
+        <v>-0.6956377431695026</v>
       </c>
       <c r="P54">
         <v>1.855382785116464</v>
@@ -33500,10 +33500,10 @@
         <v>3.436715030790507</v>
       </c>
       <c r="R54">
-        <v>-0.09560543882075422</v>
+        <v>-0.09560543882073795</v>
       </c>
       <c r="S54">
-        <v>-0.570239159683453</v>
+        <v>-0.5702391596834354</v>
       </c>
     </row>
     <row r="55">
@@ -33531,37 +33531,37 @@
         <v>-1.963781114354311</v>
       </c>
       <c r="H55">
-        <v>0.5437214258878775</v>
+        <v>0.5437214258879211</v>
       </c>
       <c r="I55">
         <v>-8.249447516329164</v>
       </c>
       <c r="J55">
-        <v>8.160345455521119</v>
+        <v>8.160345455521098</v>
       </c>
       <c r="K55">
         <v>3.407098847612814</v>
       </c>
       <c r="L55">
-        <v>2.460292248325372</v>
+        <v>2.460292248325385</v>
       </c>
       <c r="M55">
         <v>0.293295270181374</v>
       </c>
       <c r="N55">
-        <v>-7.584038403641901</v>
+        <v>-7.584038403641881</v>
       </c>
       <c r="O55">
-        <v>-1.88397797103134</v>
+        <v>-1.883977971031355</v>
       </c>
       <c r="P55">
-        <v>-2.160432011456835</v>
+        <v>-2.160432011456848</v>
       </c>
       <c r="Q55">
-        <v>-1.682967180076642</v>
+        <v>-1.682967180076658</v>
       </c>
       <c r="R55">
-        <v>-1.022563489133425</v>
+        <v>-1.022563489133393</v>
       </c>
       <c r="S55">
         <v>-1.239754134316528</v>
@@ -33574,31 +33574,31 @@
         </is>
       </c>
       <c r="B56">
-        <v>-6.780454169789892</v>
+        <v>-6.780454169789917</v>
       </c>
       <c r="C56">
-        <v>54.6779863091314</v>
+        <v>54.67798630913137</v>
       </c>
       <c r="D56">
-        <v>-1.927441978721619</v>
+        <v>-1.927441978721641</v>
       </c>
       <c r="E56">
         <v>-1.282682047866784</v>
       </c>
       <c r="F56">
-        <v>6.023189208102971</v>
+        <v>6.023189208102998</v>
       </c>
       <c r="G56">
-        <v>-0.3596788705898444</v>
+        <v>-0.359678870589832</v>
       </c>
       <c r="H56">
         <v>2.273407237557683</v>
       </c>
       <c r="I56">
-        <v>-8.534125698599583</v>
+        <v>-8.534125698599548</v>
       </c>
       <c r="J56">
-        <v>4.314759928603209</v>
+        <v>4.314759928603189</v>
       </c>
       <c r="K56">
         <v>-9.327629672350502</v>
@@ -33610,7 +33610,7 @@
         <v>-0.747643047793767</v>
       </c>
       <c r="N56">
-        <v>-5.787413708923055</v>
+        <v>-5.787413708923075</v>
       </c>
       <c r="O56">
         <v>-1.659274431819569</v>
@@ -33619,7 +33619,7 @@
         <v>-1.841230288429364</v>
       </c>
       <c r="Q56">
-        <v>-1.612060216676952</v>
+        <v>-1.612060216676936</v>
       </c>
       <c r="R56">
         <v>-0.6991199729991909</v>
@@ -33638,13 +33638,13 @@
         <v>-6.411721662888889</v>
       </c>
       <c r="C57">
-        <v>86.7556275942313</v>
+        <v>86.75562759423131</v>
       </c>
       <c r="D57">
         <v>0.7436955967009059</v>
       </c>
       <c r="E57">
-        <v>0.5916899415098695</v>
+        <v>0.5916899415098094</v>
       </c>
       <c r="F57">
         <v>4.926863558671526</v>
@@ -33659,7 +33659,7 @@
         <v>-5.150205839550174</v>
       </c>
       <c r="J57">
-        <v>5.684937958668613</v>
+        <v>5.684937958668635</v>
       </c>
       <c r="K57">
         <v>-16.87169106458133</v>
@@ -33680,7 +33680,7 @@
         <v>-1.156635307360267</v>
       </c>
       <c r="Q57">
-        <v>-0.9445670694362581</v>
+        <v>-0.9445670694362426</v>
       </c>
       <c r="R57">
         <v>0.0006462538849237508</v>
